--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_45.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5200634.421138216</v>
+        <v>5201006.772722365</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13726352.19588493</v>
+        <v>13726352.1958849</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13726352.19588493</v>
+        <v>13726352.1958849</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1664312.317955036</v>
+        <v>1667881.065193421</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1664312.317955036</v>
+        <v>1667881.065193421</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41814664.33313112</v>
+        <v>41820896.09755182</v>
       </c>
     </row>
   </sheetData>
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.570243874246615</v>
+        <v>76.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>45.47457824299391</v>
+        <v>44.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>6.339155739849787</v>
+        <v>5.339155739849787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3632896068686745</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8896287080119504</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -705,25 +705,25 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>81.87057986262442</v>
+        <v>80.87057986262442</v>
       </c>
       <c r="T2" t="n">
-        <v>180.9509787134886</v>
+        <v>179.9509787134886</v>
       </c>
       <c r="U2" t="n">
-        <v>245.189778960671</v>
+        <v>244.189778960671</v>
       </c>
       <c r="V2" t="n">
-        <v>225.8510241668239</v>
+        <v>224.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>234.3734759809475</v>
+        <v>233.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>188.2818334606677</v>
+        <v>187.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>107.3174326828064</v>
+        <v>42.1412819163586</v>
       </c>
     </row>
     <row r="3">
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5287434221972</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R3" t="n">
-        <v>130.1861746508698</v>
+        <v>340</v>
       </c>
       <c r="S3" t="n">
-        <v>58.64862260612074</v>
+        <v>231.68481833936</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5081237080793135</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="V3" t="n">
-        <v>10.51066719152016</v>
+        <v>9.510667191520156</v>
       </c>
       <c r="W3" t="n">
-        <v>28.37314290982852</v>
+        <v>27.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>279.9084897811408</v>
+        <v>14.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>88.92974255009085</v>
+        <v>87.92974255009085</v>
       </c>
       <c r="N4" t="n">
-        <v>140.1418949438161</v>
+        <v>139.1418949438161</v>
       </c>
       <c r="O4" t="n">
-        <v>211.4668099806543</v>
+        <v>210.4668099806543</v>
       </c>
       <c r="P4" t="n">
-        <v>257.236190905575</v>
+        <v>261.0742579840152</v>
       </c>
       <c r="Q4" t="n">
-        <v>307.041266425598</v>
+        <v>306.041266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>314.6560951942658</v>
+        <v>313.6560951942658</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.99931295557451</v>
+        <v>12.82316218912671</v>
       </c>
       <c r="C5" t="n">
         <v>44.47457824299391</v>
@@ -957,7 +957,7 @@
         <v>233.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>123.1056826942199</v>
+        <v>187.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>106.3174326828064</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -979,55 +979,55 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>340</v>
       </c>
-      <c r="F6" t="n">
-        <v>339.6362423378769</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>146.1717933923664</v>
-      </c>
-      <c r="R6" t="n">
-        <v>129.1861746508698</v>
-      </c>
       <c r="S6" t="n">
-        <v>57.64862260612074</v>
+        <v>247.7254504532636</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="V6" t="n">
         <v>9.510667191520156</v>
@@ -1036,7 +1036,7 @@
         <v>27.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>269.9453569114175</v>
+        <v>14.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.797449233552193</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>187.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>88.71088191635859</v>
+        <v>106.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1216,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9.510667191520156</v>
+        <v>357.000000000007</v>
       </c>
       <c r="W9" t="n">
-        <v>27.37314290982852</v>
+        <v>357.000000000007</v>
       </c>
       <c r="X9" t="n">
-        <v>103.9740209679672</v>
+        <v>128.5701706290916</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>122.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90.47457824299391</v>
+        <v>91.47457824299391</v>
       </c>
       <c r="D11" t="n">
-        <v>51.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>45.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>45.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>44.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>44.97491498493444</v>
+        <v>39.77433047440719</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1419,22 +1419,22 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>225.9509787134885</v>
+        <v>226.9509787134885</v>
       </c>
       <c r="U11" t="n">
-        <v>290.189778960671</v>
+        <v>291.189778960671</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>271.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>279.3734759809475</v>
+        <v>280.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>42.66005098608348</v>
+        <v>234.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>152.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25.55655664632661</v>
+        <v>370</v>
       </c>
       <c r="C12" t="n">
-        <v>2.099912445519294</v>
+        <v>3.099912445519294</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H12" t="n">
-        <v>323.7182851802755</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,31 +1489,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>175.1861746508699</v>
+        <v>176.1861746508699</v>
       </c>
       <c r="S12" t="n">
-        <v>103.6486226061207</v>
+        <v>104.6486226061207</v>
       </c>
       <c r="T12" t="n">
-        <v>45.50812370807985</v>
+        <v>46.50812370807985</v>
       </c>
       <c r="U12" t="n">
-        <v>41.19649183565845</v>
+        <v>42.19649183565845</v>
       </c>
       <c r="V12" t="n">
-        <v>55.51066719152016</v>
+        <v>56.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>73.37314290982852</v>
+        <v>74.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>60.86273944538755</v>
+        <v>61.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>40.39139276613435</v>
+        <v>174.9813817848728</v>
       </c>
     </row>
     <row r="13">
@@ -1559,22 +1559,22 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>185.1418949438161</v>
+        <v>155.3638612044147</v>
       </c>
       <c r="O13" t="n">
-        <v>256.4668099806543</v>
+        <v>257.4668099806543</v>
       </c>
       <c r="P13" t="n">
-        <v>307.0742579840152</v>
+        <v>308.0742579840152</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.041266425598</v>
+        <v>353.041266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>334.8780614548643</v>
+        <v>360.6560951942658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2937092110521569</v>
+        <v>1.293709211052157</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.72257874926591</v>
+        <v>53.06089617197034</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>16.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>16.97491498493444</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>44.07814058668301</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1726,22 +1726,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R15" t="n">
         <v>370</v>
       </c>
       <c r="S15" t="n">
-        <v>226.6264224372087</v>
+        <v>370</v>
       </c>
       <c r="T15" t="n">
         <v>17.50812370807985</v>
       </c>
       <c r="U15" t="n">
-        <v>13.19649183565845</v>
+        <v>370</v>
       </c>
       <c r="V15" t="n">
-        <v>370</v>
+        <v>27.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>45.37314290982852</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.585932921559627</v>
+        <v>10.27398881351688</v>
       </c>
       <c r="M16" t="n">
-        <v>105.9297425500909</v>
+        <v>105.2416866581335</v>
       </c>
       <c r="N16" t="n">
         <v>157.1418949438161</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80.65592645154176</v>
+        <v>80.99931295557451</v>
       </c>
       <c r="C17" t="n">
         <v>48.47457824299391</v>
@@ -1854,10 +1854,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G17" t="n">
-        <v>2.363402437769979</v>
+        <v>2.363402437769992</v>
       </c>
       <c r="H17" t="n">
-        <v>2.974914984934444</v>
+        <v>2.974914984934458</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,16 +1890,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>84.87057986262441</v>
+        <v>84.87057986262442</v>
       </c>
       <c r="T17" t="n">
-        <v>183.9509787134885</v>
+        <v>183.9509787134886</v>
       </c>
       <c r="U17" t="n">
         <v>248.189778960671</v>
       </c>
       <c r="V17" t="n">
-        <v>228.8510241668239</v>
+        <v>228.5076376627911</v>
       </c>
       <c r="W17" t="n">
         <v>237.3734759809475</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>296.5348236503075</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1966,19 +1966,19 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R18" t="n">
-        <v>133.1861746508699</v>
+        <v>133.1861746508698</v>
       </c>
       <c r="S18" t="n">
-        <v>61.64862260612073</v>
+        <v>61.64862260612074</v>
       </c>
       <c r="T18" t="n">
-        <v>304.6535269954268</v>
+        <v>3.508123708079836</v>
       </c>
       <c r="U18" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>370</v>
+        <v>13.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>31.37314290982852</v>
@@ -1987,7 +1987,7 @@
         <v>18.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19">
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>91.92974255009086</v>
+        <v>91.92974255009085</v>
       </c>
       <c r="N19" t="n">
         <v>143.1418949438161</v>
@@ -2091,10 +2091,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>2.020015933737224</v>
+        <v>2.363402437769979</v>
       </c>
       <c r="H20" t="n">
-        <v>2.974914984934458</v>
+        <v>2.974914984934444</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>84.87057986262442</v>
+        <v>84.87057986262441</v>
       </c>
       <c r="T20" t="n">
-        <v>183.9509787134886</v>
+        <v>183.9509787134885</v>
       </c>
       <c r="U20" t="n">
-        <v>248.189778960671</v>
+        <v>247.8463924566382</v>
       </c>
       <c r="V20" t="n">
         <v>228.8510241668239</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>122.0968329230588</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>330.1322758656664</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>133.1861746508698</v>
+        <v>370</v>
       </c>
       <c r="S21" t="n">
-        <v>61.64862260612074</v>
+        <v>61.64862260612073</v>
       </c>
       <c r="T21" t="n">
-        <v>3.508123708079836</v>
+        <v>284.8398085592796</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>91.92974255009085</v>
+        <v>91.92974255009086</v>
       </c>
       <c r="N22" t="n">
         <v>143.1418949438161</v>
@@ -2328,10 +2328,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G23" t="n">
-        <v>2.020015933737224</v>
+        <v>2.363402437769979</v>
       </c>
       <c r="H23" t="n">
-        <v>2.974914984934458</v>
+        <v>2.974914984934444</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>84.87057986262442</v>
+        <v>84.87057986262441</v>
       </c>
       <c r="T23" t="n">
-        <v>183.9509787134886</v>
+        <v>183.9509787134885</v>
       </c>
       <c r="U23" t="n">
         <v>248.189778960671</v>
       </c>
       <c r="V23" t="n">
-        <v>228.8510241668239</v>
+        <v>228.5076376628748</v>
       </c>
       <c r="W23" t="n">
         <v>237.3734759809475</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>125.1326878071783</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2437,31 +2437,31 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>133.1861746508698</v>
+        <v>133.1861746508699</v>
       </c>
       <c r="S24" t="n">
-        <v>61.64862260612074</v>
+        <v>61.64862260612073</v>
       </c>
       <c r="T24" t="n">
-        <v>3.508123708079836</v>
+        <v>3.508123708079854</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>332.5185461971755</v>
+        <v>13.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>370</v>
+        <v>31.37314290982852</v>
       </c>
       <c r="X24" t="n">
         <v>18.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>91.92974255009085</v>
+        <v>91.92974255009086</v>
       </c>
       <c r="N25" t="n">
         <v>143.1418949438161</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>169.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>137.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>98.33915573984979</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>92.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>91.97491498493444</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,25 +2601,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>173.8705798626244</v>
       </c>
       <c r="T26" t="n">
-        <v>241.2872921835456</v>
+        <v>272.9509787134885</v>
       </c>
       <c r="U26" t="n">
-        <v>337.189778960671</v>
+        <v>171.6642468177279</v>
       </c>
       <c r="V26" t="n">
-        <v>317.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>326.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>199.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2647,7 +2647,7 @@
         <v>13.52874342219715</v>
       </c>
       <c r="H27" t="n">
-        <v>18.13227586566641</v>
+        <v>114.4826059148654</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>96.35033004919882</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>222.1861746508699</v>
@@ -2747,16 +2747,16 @@
         <v>232.1418949438161</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>303.4668099806543</v>
       </c>
       <c r="P28" t="n">
-        <v>339</v>
+        <v>339.0000000000715</v>
       </c>
       <c r="Q28" t="n">
-        <v>339</v>
+        <v>121.7395496001121</v>
       </c>
       <c r="R28" t="n">
-        <v>86.20635958083791</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>47.29370921105216</v>
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>169.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>137.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>98.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>53.8950874308898</v>
       </c>
       <c r="F29" t="n">
-        <v>92.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>10.91578222914815</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2844,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>337.189778960671</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>317.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>326.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>280.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>199.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2878,16 +2878,16 @@
         <v>30.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>27.63624233787687</v>
+        <v>123.9865723870758</v>
       </c>
       <c r="G30" t="n">
-        <v>13.52874342219718</v>
+        <v>13.52874342219715</v>
       </c>
       <c r="H30" t="n">
-        <v>18.13227586566643</v>
+        <v>18.13227586566641</v>
       </c>
       <c r="I30" t="n">
-        <v>96.35033004919902</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>222.1861746508698</v>
+        <v>222.1861746508699</v>
       </c>
       <c r="S30" t="n">
         <v>150.6486226061207</v>
       </c>
       <c r="T30" t="n">
-        <v>92.50812370807984</v>
+        <v>92.50812370807985</v>
       </c>
       <c r="U30" t="n">
-        <v>88.19649183565843</v>
+        <v>88.19649183565845</v>
       </c>
       <c r="V30" t="n">
         <v>102.5106671915202</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>85.27398881351689</v>
+        <v>85.27398881351688</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2987,16 +2987,16 @@
         <v>303.4668099806543</v>
       </c>
       <c r="P31" t="n">
-        <v>302.6692921502744</v>
+        <v>339.0000000000115</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>302.6692921502627</v>
       </c>
       <c r="R31" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>47.29370921105215</v>
+        <v>47.29370921105216</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>16.71260497340189</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>66.87057986262441</v>
+        <v>64.17918483602648</v>
       </c>
       <c r="T32" t="n">
         <v>165.9509787134885</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R33" t="n">
-        <v>115.1861746508699</v>
+        <v>191.6924629247595</v>
       </c>
       <c r="S33" t="n">
         <v>43.64862260612073</v>
@@ -3160,16 +3160,16 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>327</v>
+        <v>13.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>129.1868027430094</v>
+        <v>0.8627394453875468</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0.8582049734021348</v>
       </c>
       <c r="S35" t="n">
-        <v>60.87057986262442</v>
+        <v>60.87057986262441</v>
       </c>
       <c r="T35" t="n">
-        <v>159.9509787134886</v>
+        <v>159.9509787134885</v>
       </c>
       <c r="U35" t="n">
         <v>224.189778960671</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>280.7874664407921</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>309.0000000000111</v>
       </c>
       <c r="G36" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3385,13 +3385,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R36" t="n">
-        <v>309</v>
+        <v>109.1861746508699</v>
       </c>
       <c r="S36" t="n">
-        <v>264.7940570901715</v>
+        <v>37.64862260612073</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>309.0000000000111</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>67.92974255009085</v>
+        <v>67.92974255009086</v>
       </c>
       <c r="N37" t="n">
         <v>119.1418949438161</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3589,16 +3589,16 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R39" t="n">
-        <v>309</v>
+        <v>109.1861746508699</v>
       </c>
       <c r="S39" t="n">
-        <v>309</v>
+        <v>108.5672503253763</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>118.622263697805</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>7.373142909828516</v>
@@ -3735,19 +3735,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>164.1005477021983</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>136.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>97.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>91.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2162212865114551</v>
+        <v>91.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3789,16 +3789,16 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>271.9509787134885</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>309</v>
+        <v>309.0000000000414</v>
       </c>
       <c r="V41" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>309</v>
+        <v>309.000000000036</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>26.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>7.455073471396043</v>
+        <v>12.52874342219715</v>
       </c>
       <c r="H42" t="n">
         <v>17.13227586566641</v>
@@ -3865,7 +3865,7 @@
         <v>221.1861746508699</v>
       </c>
       <c r="S42" t="n">
-        <v>149.6486226061207</v>
+        <v>144.5749526553195</v>
       </c>
       <c r="T42" t="n">
         <v>91.50812370807985</v>
@@ -3923,28 +3923,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>84.27398881351688</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>179.9297425500909</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>231.1418949438161</v>
       </c>
       <c r="O43" t="n">
-        <v>272.1671999999999</v>
+        <v>302.4668099806543</v>
       </c>
       <c r="P43" t="n">
-        <v>309</v>
+        <v>46.06105450077069</v>
       </c>
       <c r="Q43" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>309</v>
+        <v>309.0000000000991</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>46.29370921105216</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>197.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>164.4745782429939</v>
+        <v>165.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>125.3391557398498</v>
+        <v>126.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>119.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>91.35415306155994</v>
       </c>
       <c r="H44" t="n">
-        <v>118.9749149849344</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,19 +4023,19 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>200.8705798626244</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>309</v>
+        <v>309.000000000011</v>
       </c>
       <c r="V44" t="n">
-        <v>161.1446815627286</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>309.000000000011</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>99.55655664632661</v>
+        <v>100.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>76.09991244551929</v>
+        <v>77.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>62.93768689770263</v>
+        <v>63.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>57.67209722191262</v>
+        <v>58.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>54.63624233787687</v>
+        <v>55.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>40.52874342219715</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>45.13227586566641</v>
+        <v>46.13227586566643</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>178.6630136382152</v>
       </c>
       <c r="S45" t="n">
-        <v>1.761127306189382</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>119.5081237080799</v>
+        <v>120.5081237080798</v>
       </c>
       <c r="U45" t="n">
-        <v>115.1964918356584</v>
+        <v>116.1964918356584</v>
       </c>
       <c r="V45" t="n">
-        <v>129.5106671915202</v>
+        <v>130.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>147.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>134.8627394453875</v>
+        <v>135.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>114.3913927661343</v>
+        <v>115.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5362180555554801</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>112.2739888135169</v>
+        <v>113.2739888135169</v>
       </c>
       <c r="M46" t="n">
-        <v>207.9297425500909</v>
+        <v>208.9297425500909</v>
       </c>
       <c r="N46" t="n">
-        <v>259.1418949438161</v>
+        <v>260.1418949438161</v>
       </c>
       <c r="O46" t="n">
-        <v>235.1667165425823</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>296.3691441462685</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>74.29370921105216</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.80267908860982</v>
+        <v>77.51690301297344</v>
       </c>
       <c r="C2" t="n">
-        <v>34.86876167144425</v>
+        <v>32.59308660590887</v>
       </c>
       <c r="D2" t="n">
-        <v>28.46557405543436</v>
+        <v>27.2</v>
       </c>
       <c r="E2" t="n">
-        <v>28.09861485657763</v>
+        <v>27.2</v>
       </c>
       <c r="F2" t="n">
         <v>27.2</v>
@@ -4324,7 +4324,7 @@
         <v>27.2</v>
       </c>
       <c r="K2" t="n">
-        <v>76.81329778894472</v>
+        <v>232.8476832091187</v>
       </c>
       <c r="L2" t="n">
         <v>294.3973662241941</v>
@@ -4348,25 +4348,25 @@
         <v>1360</v>
       </c>
       <c r="S2" t="n">
-        <v>1277.302444583208</v>
+        <v>1278.312545593309</v>
       </c>
       <c r="T2" t="n">
-        <v>1094.523678205946</v>
+        <v>1096.543880226149</v>
       </c>
       <c r="U2" t="n">
-        <v>846.8572348113292</v>
+        <v>849.8875378416324</v>
       </c>
       <c r="V2" t="n">
-        <v>618.7248871680728</v>
+        <v>622.7652912084769</v>
       </c>
       <c r="W2" t="n">
-        <v>381.9840023388328</v>
+        <v>387.0345073893379</v>
       </c>
       <c r="X2" t="n">
-        <v>191.8003321765422</v>
+        <v>197.8609382371483</v>
       </c>
       <c r="Y2" t="n">
-        <v>83.39888502219226</v>
+        <v>155.293986806483</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="C3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="D3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="E3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="F3" t="n">
-        <v>356.0169125476739</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="G3" t="n">
-        <v>27.2</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="H3" t="n">
-        <v>27.2</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="I3" t="n">
         <v>27.2</v>
@@ -4403,16 +4403,16 @@
         <v>170.8726316847329</v>
       </c>
       <c r="K3" t="n">
-        <v>275.7536123162412</v>
+        <v>393.7634226847767</v>
       </c>
       <c r="L3" t="n">
-        <v>592.4151597604979</v>
+        <v>710.4249701290335</v>
       </c>
       <c r="M3" t="n">
-        <v>731.3716015033571</v>
+        <v>849.3814118718926</v>
       </c>
       <c r="N3" t="n">
-        <v>918.9272538467744</v>
+        <v>1036.93706421531</v>
       </c>
       <c r="O3" t="n">
         <v>1207.621063455022</v>
@@ -4424,28 +4424,28 @@
         <v>1212.351723846095</v>
       </c>
       <c r="R3" t="n">
-        <v>1080.850537330064</v>
+        <v>868.9173804117511</v>
       </c>
       <c r="S3" t="n">
-        <v>1021.609504394589</v>
+        <v>634.8923113820945</v>
       </c>
       <c r="T3" t="n">
-        <v>1021.096248123802</v>
+        <v>634.8923113820945</v>
       </c>
       <c r="U3" t="n">
-        <v>1021.096248123802</v>
+        <v>291.4579679477509</v>
       </c>
       <c r="V3" t="n">
-        <v>1010.479412576812</v>
+        <v>281.8512334108619</v>
       </c>
       <c r="W3" t="n">
-        <v>981.8196722638535</v>
+        <v>254.2015941080048</v>
       </c>
       <c r="X3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
       <c r="Y3" t="n">
-        <v>699.0838240000749</v>
+        <v>239.1887259813507</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>663.7981649586242</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="C4" t="n">
-        <v>793.76017077706</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="D4" t="n">
-        <v>793.76017077706</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="E4" t="n">
-        <v>793.76017077706</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="F4" t="n">
-        <v>793.76017077706</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="G4" t="n">
-        <v>841.7091627823776</v>
+        <v>607.2112673433115</v>
       </c>
       <c r="H4" t="n">
-        <v>1016.741248925382</v>
+        <v>783.2333534863157</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.741248925382</v>
+        <v>1014.577579307644</v>
       </c>
       <c r="J4" t="n">
-        <v>1353.341248925382</v>
+        <v>1351.177579307644</v>
       </c>
       <c r="K4" t="n">
-        <v>1353.341248925382</v>
+        <v>1351.177579307644</v>
       </c>
       <c r="L4" t="n">
-        <v>1360</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="M4" t="n">
-        <v>1270.17197722213</v>
+        <v>1270.008408614494</v>
       </c>
       <c r="N4" t="n">
-        <v>1128.614507581912</v>
+        <v>1129.461039984377</v>
       </c>
       <c r="O4" t="n">
-        <v>915.011669217615</v>
+        <v>916.8683026301808</v>
       </c>
       <c r="P4" t="n">
-        <v>655.1771329493574</v>
+        <v>653.1569309291554</v>
       </c>
       <c r="Q4" t="n">
-        <v>345.0344395901676</v>
+        <v>344.0243385800665</v>
       </c>
       <c r="R4" t="n">
         <v>27.2</v>
@@ -4509,22 +4509,22 @@
         <v>27.2</v>
       </c>
       <c r="T4" t="n">
-        <v>27.2</v>
+        <v>220.9732103063458</v>
       </c>
       <c r="U4" t="n">
-        <v>277.7207355891063</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="V4" t="n">
-        <v>277.7207355891063</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="W4" t="n">
-        <v>277.7207355891063</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="X4" t="n">
-        <v>432.7115266132998</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="Y4" t="n">
-        <v>548.0808272923321</v>
+        <v>472.4839458954522</v>
       </c>
     </row>
     <row r="5">
@@ -4600,10 +4600,10 @@
         <v>387.0345073893379</v>
       </c>
       <c r="X5" t="n">
-        <v>262.6853329507319</v>
+        <v>197.8609382371483</v>
       </c>
       <c r="Y5" t="n">
-        <v>155.293986806483</v>
+        <v>90.46959209289942</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>713.7012548867443</v>
+        <v>27.2</v>
       </c>
       <c r="C6" t="n">
-        <v>713.7012548867443</v>
+        <v>27.2</v>
       </c>
       <c r="D6" t="n">
-        <v>713.7012548867443</v>
+        <v>27.2</v>
       </c>
       <c r="E6" t="n">
-        <v>370.2669114524008</v>
+        <v>27.2</v>
       </c>
       <c r="F6" t="n">
         <v>27.2</v>
@@ -4637,10 +4637,10 @@
         <v>27.2</v>
       </c>
       <c r="J6" t="n">
-        <v>170.8726316847329</v>
+        <v>52.8628213161974</v>
       </c>
       <c r="K6" t="n">
-        <v>393.7634226847767</v>
+        <v>275.7536123162412</v>
       </c>
       <c r="L6" t="n">
         <v>592.4151597604979</v>
@@ -4658,31 +4658,31 @@
         <v>1360</v>
       </c>
       <c r="Q6" t="n">
-        <v>1212.351723846095</v>
+        <v>1360</v>
       </c>
       <c r="R6" t="n">
-        <v>1081.860638340165</v>
+        <v>1016.565656565657</v>
       </c>
       <c r="S6" t="n">
-        <v>1023.629706414791</v>
+        <v>766.3379288350873</v>
       </c>
       <c r="T6" t="n">
-        <v>1023.629706414791</v>
+        <v>766.3379288350873</v>
       </c>
       <c r="U6" t="n">
-        <v>1023.629706414791</v>
+        <v>422.9035854007437</v>
       </c>
       <c r="V6" t="n">
-        <v>1014.022971877902</v>
+        <v>413.2968508638547</v>
       </c>
       <c r="W6" t="n">
-        <v>986.3733325750449</v>
+        <v>385.6472115609976</v>
       </c>
       <c r="X6" t="n">
-        <v>713.7012548867443</v>
+        <v>370.6343434343435</v>
       </c>
       <c r="Y6" t="n">
-        <v>713.7012548867443</v>
+        <v>370.6343434343435</v>
       </c>
     </row>
     <row r="7">
@@ -4692,22 +4692,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>659.3230467347297</v>
+        <v>1229.515357790327</v>
       </c>
       <c r="C7" t="n">
-        <v>659.3230467347297</v>
+        <v>1229.515357790327</v>
       </c>
       <c r="D7" t="n">
-        <v>777.5921908597297</v>
+        <v>1229.515357790327</v>
       </c>
       <c r="E7" t="n">
-        <v>900.3710950711427</v>
+        <v>1229.515357790327</v>
       </c>
       <c r="F7" t="n">
-        <v>1029.682067663078</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="G7" t="n">
-        <v>1188.213587648324</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="H7" t="n">
         <v>1358.826330382263</v>
@@ -4743,25 +4743,25 @@
         <v>27.2</v>
       </c>
       <c r="S7" t="n">
-        <v>27.2</v>
+        <v>72.44922788105838</v>
       </c>
       <c r="T7" t="n">
-        <v>27.2</v>
+        <v>266.2224381874042</v>
       </c>
       <c r="U7" t="n">
-        <v>278.7107355891063</v>
+        <v>517.7331737765105</v>
       </c>
       <c r="V7" t="n">
-        <v>482.4821284750523</v>
+        <v>721.5045666624565</v>
       </c>
       <c r="W7" t="n">
-        <v>659.3230467347297</v>
+        <v>898.3454849221339</v>
       </c>
       <c r="X7" t="n">
-        <v>659.3230467347297</v>
+        <v>1054.326275946327</v>
       </c>
       <c r="Y7" t="n">
-        <v>659.3230467347297</v>
+        <v>1170.68557662536</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.47690301297344</v>
+        <v>80.6925082993898</v>
       </c>
       <c r="C8" t="n">
-        <v>33.55308660590887</v>
+        <v>35.76869189232524</v>
       </c>
       <c r="D8" t="n">
-        <v>28.16</v>
+        <v>30.37560528641636</v>
       </c>
       <c r="E8" t="n">
-        <v>28.16</v>
+        <v>30.37560528641636</v>
       </c>
       <c r="F8" t="n">
-        <v>28.16</v>
+        <v>30.37560528641636</v>
       </c>
       <c r="G8" t="n">
-        <v>28.16</v>
+        <v>30.37560528641636</v>
       </c>
       <c r="H8" t="n">
-        <v>28.16</v>
+        <v>28.56</v>
       </c>
       <c r="I8" t="n">
-        <v>28.16</v>
+        <v>28.56</v>
       </c>
       <c r="J8" t="n">
-        <v>376.6400000000008</v>
+        <v>28.56</v>
       </c>
       <c r="K8" t="n">
-        <v>426.2532977889456</v>
+        <v>381.99</v>
       </c>
       <c r="L8" t="n">
-        <v>774.7332977889455</v>
+        <v>735.42</v>
       </c>
       <c r="M8" t="n">
-        <v>1123.213297788946</v>
+        <v>1088.850000000007</v>
       </c>
       <c r="N8" t="n">
-        <v>1352.197366224194</v>
+        <v>1088.850000000007</v>
       </c>
       <c r="O8" t="n">
-        <v>1352.197366224194</v>
+        <v>1088.850000000007</v>
       </c>
       <c r="P8" t="n">
-        <v>1408</v>
+        <v>1144.652633775813</v>
       </c>
       <c r="Q8" t="n">
-        <v>1408</v>
+        <v>1428</v>
       </c>
       <c r="R8" t="n">
-        <v>1408</v>
+        <v>1428</v>
       </c>
       <c r="S8" t="n">
-        <v>1326.312545593309</v>
+        <v>1346.312545593309</v>
       </c>
       <c r="T8" t="n">
-        <v>1144.543880226149</v>
+        <v>1164.543880226149</v>
       </c>
       <c r="U8" t="n">
-        <v>897.8875378416324</v>
+        <v>917.8875378416324</v>
       </c>
       <c r="V8" t="n">
-        <v>670.7652912084769</v>
+        <v>690.7652912084769</v>
       </c>
       <c r="W8" t="n">
-        <v>435.0345073893379</v>
+        <v>455.0345073893379</v>
       </c>
       <c r="X8" t="n">
-        <v>245.8609382371483</v>
+        <v>265.8609382371483</v>
       </c>
       <c r="Y8" t="n">
-        <v>156.2539868064831</v>
+        <v>158.4695920928994</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>929.3490689710372</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="C9" t="n">
-        <v>929.3490689710372</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="D9" t="n">
-        <v>929.3490689710372</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="E9" t="n">
-        <v>583.2156374337517</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="F9" t="n">
-        <v>240.1487259813507</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="G9" t="n">
-        <v>240.1487259813507</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="H9" t="n">
-        <v>240.1487259813507</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="I9" t="n">
-        <v>28.16</v>
+        <v>28.56</v>
       </c>
       <c r="J9" t="n">
-        <v>171.8326316847329</v>
+        <v>120.8628213161974</v>
       </c>
       <c r="K9" t="n">
-        <v>394.7234226847767</v>
+        <v>343.7536123162412</v>
       </c>
       <c r="L9" t="n">
-        <v>640.4151597604979</v>
+        <v>660.4151597604979</v>
       </c>
       <c r="M9" t="n">
-        <v>779.3716015033571</v>
+        <v>799.3716015033571</v>
       </c>
       <c r="N9" t="n">
-        <v>966.9272538467744</v>
+        <v>986.9272538467744</v>
       </c>
       <c r="O9" t="n">
-        <v>1255.621063455022</v>
+        <v>1275.621063455022</v>
       </c>
       <c r="P9" t="n">
-        <v>1408</v>
+        <v>1428</v>
       </c>
       <c r="Q9" t="n">
-        <v>1260.351723846095</v>
+        <v>1280.351723846095</v>
       </c>
       <c r="R9" t="n">
-        <v>1129.860638340165</v>
+        <v>1149.860638340165</v>
       </c>
       <c r="S9" t="n">
-        <v>1071.629706414791</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="T9" t="n">
-        <v>1071.629706414791</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="U9" t="n">
-        <v>1071.629706414791</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="V9" t="n">
-        <v>1062.022971877902</v>
+        <v>731.023645808723</v>
       </c>
       <c r="W9" t="n">
-        <v>1034.373332575045</v>
+        <v>370.4175852026553</v>
       </c>
       <c r="X9" t="n">
-        <v>929.3490689710372</v>
+        <v>240.5487259813507</v>
       </c>
       <c r="Y9" t="n">
-        <v>929.3490689710372</v>
+        <v>240.5487259813507</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1243.103686410594</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="C10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="D10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="E10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="F10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="G10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="H10" t="n">
-        <v>1359.786330382263</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="I10" t="n">
-        <v>1359.786330382263</v>
+        <v>863.4666601248678</v>
       </c>
       <c r="J10" t="n">
-        <v>1359.786330382263</v>
+        <v>1216.896660124875</v>
       </c>
       <c r="K10" t="n">
-        <v>1359.786330382263</v>
+        <v>1352.537579307645</v>
       </c>
       <c r="L10" t="n">
-        <v>1359.786330382263</v>
+        <v>1360.186330382263</v>
       </c>
       <c r="M10" t="n">
-        <v>1270.968408614494</v>
+        <v>1271.368408614494</v>
       </c>
       <c r="N10" t="n">
-        <v>1130.421039984377</v>
+        <v>1130.821039984377</v>
       </c>
       <c r="O10" t="n">
-        <v>917.8283026301808</v>
+        <v>918.2283026301808</v>
       </c>
       <c r="P10" t="n">
-        <v>654.1169309291554</v>
+        <v>654.5169309291554</v>
       </c>
       <c r="Q10" t="n">
-        <v>344.9843385800665</v>
+        <v>345.3843385800665</v>
       </c>
       <c r="R10" t="n">
-        <v>28.16</v>
+        <v>28.56</v>
       </c>
       <c r="S10" t="n">
-        <v>28.16</v>
+        <v>28.56</v>
       </c>
       <c r="T10" t="n">
-        <v>221.9332103063458</v>
+        <v>28.56</v>
       </c>
       <c r="U10" t="n">
-        <v>473.4439458954521</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="V10" t="n">
-        <v>677.2153387813981</v>
+        <v>483.8421284750523</v>
       </c>
       <c r="W10" t="n">
-        <v>854.0562570410756</v>
+        <v>660.6830467347297</v>
       </c>
       <c r="X10" t="n">
-        <v>1010.037048065269</v>
+        <v>816.6638377589233</v>
       </c>
       <c r="Y10" t="n">
-        <v>1126.396348744301</v>
+        <v>816.6638377589233</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>355.2615855761906</v>
+        <v>162.1746552701021</v>
       </c>
       <c r="C11" t="n">
-        <v>263.8731227044795</v>
+        <v>69.7760913882901</v>
       </c>
       <c r="D11" t="n">
-        <v>212.0153896339242</v>
+        <v>69.7760913882901</v>
       </c>
       <c r="E11" t="n">
-        <v>166.1938849805215</v>
+        <v>69.7760913882901</v>
       </c>
       <c r="F11" t="n">
-        <v>119.8407246693984</v>
+        <v>69.7760913882901</v>
       </c>
       <c r="G11" t="n">
-        <v>75.02920705548934</v>
+        <v>69.7760913882901</v>
       </c>
       <c r="H11" t="n">
         <v>29.6</v>
@@ -5062,22 +5062,22 @@
         <v>1480</v>
       </c>
       <c r="T11" t="n">
-        <v>1251.766688168193</v>
+        <v>1250.756587158092</v>
       </c>
       <c r="U11" t="n">
-        <v>958.6456993190309</v>
+        <v>956.6254972988287</v>
       </c>
       <c r="V11" t="n">
-        <v>958.6456993190309</v>
+        <v>682.0285031909257</v>
       </c>
       <c r="W11" t="n">
-        <v>676.4502690352455</v>
+        <v>398.8229718970392</v>
       </c>
       <c r="X11" t="n">
-        <v>633.359308443242</v>
+        <v>162.1746552701021</v>
       </c>
       <c r="Y11" t="n">
-        <v>479.5033158343466</v>
+        <v>162.1746552701021</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>704.8427220683914</v>
+        <v>361.5481372401177</v>
       </c>
       <c r="C12" t="n">
-        <v>702.7215983860486</v>
+        <v>358.416912547674</v>
       </c>
       <c r="D12" t="n">
-        <v>702.7215983860486</v>
+        <v>358.416912547674</v>
       </c>
       <c r="E12" t="n">
-        <v>356.5881668487631</v>
+        <v>358.416912547674</v>
       </c>
       <c r="F12" t="n">
-        <v>356.5881668487631</v>
+        <v>358.416912547674</v>
       </c>
       <c r="G12" t="n">
-        <v>356.5881668487631</v>
+        <v>29.6</v>
       </c>
       <c r="H12" t="n">
         <v>29.6</v>
@@ -5123,40 +5123,40 @@
         <v>851.7814118718926</v>
       </c>
       <c r="N12" t="n">
-        <v>1038.927253846774</v>
+        <v>1039.33706421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1327.621063455022</v>
+        <v>1327.621063455076</v>
       </c>
       <c r="P12" t="n">
-        <v>1480</v>
+        <v>1480.000000000055</v>
       </c>
       <c r="Q12" t="n">
-        <v>1332.351723846095</v>
+        <v>1480.000000000055</v>
       </c>
       <c r="R12" t="n">
-        <v>1155.395991875519</v>
+        <v>1302.034167019378</v>
       </c>
       <c r="S12" t="n">
-        <v>1050.700413485498</v>
+        <v>1196.328487619256</v>
       </c>
       <c r="T12" t="n">
-        <v>1004.732611760165</v>
+        <v>1149.350584883822</v>
       </c>
       <c r="U12" t="n">
-        <v>963.1199937443481</v>
+        <v>1106.727865857905</v>
       </c>
       <c r="V12" t="n">
-        <v>907.0486127428126</v>
+        <v>1049.646383846268</v>
       </c>
       <c r="W12" t="n">
-        <v>832.934326975309</v>
+        <v>974.5219970686635</v>
       </c>
       <c r="X12" t="n">
-        <v>771.4568123840085</v>
+        <v>912.0343814672619</v>
       </c>
       <c r="Y12" t="n">
-        <v>730.6574257515496</v>
+        <v>735.2855109774914</v>
       </c>
     </row>
     <row r="13">
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>925.7636864105934</v>
+        <v>604.4021597972936</v>
       </c>
       <c r="C13" t="n">
-        <v>1011.175692229029</v>
+        <v>688.8241656157294</v>
       </c>
       <c r="D13" t="n">
-        <v>1083.904836354029</v>
+        <v>760.5633097407294</v>
       </c>
       <c r="E13" t="n">
-        <v>1161.143740565442</v>
+        <v>760.5633097407294</v>
       </c>
       <c r="F13" t="n">
-        <v>1244.914713157378</v>
+        <v>843.3442823326649</v>
       </c>
       <c r="G13" t="n">
-        <v>1357.906233142624</v>
+        <v>955.3458023179107</v>
       </c>
       <c r="H13" t="n">
-        <v>1389.89908081723</v>
+        <v>1084.837888460915</v>
       </c>
       <c r="I13" t="n">
-        <v>1389.89908081723</v>
+        <v>1084.837888460915</v>
       </c>
       <c r="J13" t="n">
-        <v>1389.89908081723</v>
+        <v>1390.88908081723</v>
       </c>
       <c r="K13" t="n">
         <v>1480</v>
@@ -5202,40 +5202,40 @@
         <v>1480</v>
       </c>
       <c r="N13" t="n">
-        <v>1292.987984905236</v>
+        <v>1323.066806864228</v>
       </c>
       <c r="O13" t="n">
-        <v>1033.930601086394</v>
+        <v>1062.999322035284</v>
       </c>
       <c r="P13" t="n">
-        <v>723.7545829207218</v>
+        <v>751.813202859511</v>
       </c>
       <c r="Q13" t="n">
-        <v>368.1573441069864</v>
+        <v>395.2058630356747</v>
       </c>
       <c r="R13" t="n">
-        <v>29.89667597075976</v>
+        <v>30.90677698086077</v>
       </c>
       <c r="S13" t="n">
         <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>177.8332103063458</v>
+        <v>176.8432103063458</v>
       </c>
       <c r="U13" t="n">
-        <v>383.8039458954521</v>
+        <v>176.8432103063458</v>
       </c>
       <c r="V13" t="n">
-        <v>542.0353387813981</v>
+        <v>334.0846031922918</v>
       </c>
       <c r="W13" t="n">
-        <v>673.3362570410754</v>
+        <v>464.3955214519692</v>
       </c>
       <c r="X13" t="n">
-        <v>783.777048065269</v>
+        <v>464.3955214519692</v>
       </c>
       <c r="Y13" t="n">
-        <v>854.5963487443013</v>
+        <v>534.2248221310015</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63.27506810374185</v>
+        <v>29.6</v>
       </c>
       <c r="C14" t="n">
-        <v>63.27506810374185</v>
+        <v>29.6</v>
       </c>
       <c r="D14" t="n">
-        <v>63.27506810374185</v>
+        <v>29.6</v>
       </c>
       <c r="E14" t="n">
-        <v>63.27506810374185</v>
+        <v>29.6</v>
       </c>
       <c r="F14" t="n">
-        <v>63.27506810374185</v>
+        <v>29.6</v>
       </c>
       <c r="G14" t="n">
-        <v>46.74637877266106</v>
+        <v>29.6</v>
       </c>
       <c r="H14" t="n">
         <v>29.6</v>
@@ -5269,22 +5269,22 @@
         <v>29.6</v>
       </c>
       <c r="J14" t="n">
-        <v>29.6</v>
+        <v>395.9</v>
       </c>
       <c r="K14" t="n">
-        <v>263.7476832091189</v>
+        <v>445.5132977889448</v>
       </c>
       <c r="L14" t="n">
-        <v>325.2973662241943</v>
+        <v>507.0629808040202</v>
       </c>
       <c r="M14" t="n">
-        <v>691.5973662241943</v>
+        <v>507.0629808040202</v>
       </c>
       <c r="N14" t="n">
-        <v>1057.897366224194</v>
+        <v>747.4000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>1057.897366224194</v>
+        <v>747.4000000000001</v>
       </c>
       <c r="P14" t="n">
         <v>1113.7</v>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>381.0522089875785</v>
+        <v>29.6</v>
       </c>
       <c r="C15" t="n">
-        <v>381.0522089875785</v>
+        <v>29.6</v>
       </c>
       <c r="D15" t="n">
         <v>29.6</v>
@@ -5369,31 +5369,31 @@
         <v>1480</v>
       </c>
       <c r="Q15" t="n">
-        <v>1480</v>
+        <v>1332.351723846095</v>
       </c>
       <c r="R15" t="n">
-        <v>1106.262626262626</v>
+        <v>958.6143501087207</v>
       </c>
       <c r="S15" t="n">
-        <v>877.3470480432236</v>
+        <v>584.8769763713469</v>
       </c>
       <c r="T15" t="n">
-        <v>859.6620746007187</v>
+        <v>567.192002928842</v>
       </c>
       <c r="U15" t="n">
-        <v>846.3322848677304</v>
+        <v>193.4546291914683</v>
       </c>
       <c r="V15" t="n">
-        <v>472.5949111303566</v>
+        <v>165.666076472761</v>
       </c>
       <c r="W15" t="n">
-        <v>426.7634536456814</v>
+        <v>119.8346189880858</v>
       </c>
       <c r="X15" t="n">
-        <v>393.5687673372091</v>
+        <v>86.63993267961349</v>
       </c>
       <c r="Y15" t="n">
-        <v>381.0522089875785</v>
+        <v>74.12337432998284</v>
       </c>
     </row>
     <row r="16">
@@ -5403,37 +5403,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1147.232914291652</v>
+        <v>1048.34557662536</v>
       </c>
       <c r="C16" t="n">
-        <v>1260.364920110087</v>
+        <v>1048.34557662536</v>
       </c>
       <c r="D16" t="n">
-        <v>1260.364920110087</v>
+        <v>1069.595421279814</v>
       </c>
       <c r="E16" t="n">
-        <v>1362.17908081723</v>
+        <v>1069.595421279814</v>
       </c>
       <c r="F16" t="n">
-        <v>1362.17908081723</v>
+        <v>1181.08639387175</v>
       </c>
       <c r="G16" t="n">
-        <v>1362.17908081723</v>
+        <v>1321.797913856996</v>
       </c>
       <c r="H16" t="n">
-        <v>1362.17908081723</v>
+        <v>1480</v>
       </c>
       <c r="I16" t="n">
-        <v>1362.17908081723</v>
+        <v>1480</v>
       </c>
       <c r="J16" t="n">
-        <v>1362.17908081723</v>
+        <v>1480</v>
       </c>
       <c r="K16" t="n">
         <v>1480</v>
       </c>
       <c r="L16" t="n">
-        <v>1470.317239473172</v>
+        <v>1469.6222335217</v>
       </c>
       <c r="M16" t="n">
         <v>1363.317499523585</v>
@@ -5485,19 +5485,19 @@
         <v>100.716131030736</v>
       </c>
       <c r="C17" t="n">
-        <v>51.75191058326739</v>
+        <v>51.75191058326742</v>
       </c>
       <c r="D17" t="n">
-        <v>42.31841993695447</v>
+        <v>42.3184199369545</v>
       </c>
       <c r="E17" t="n">
-        <v>38.92115770779422</v>
+        <v>38.92115770779425</v>
       </c>
       <c r="F17" t="n">
-        <v>34.99223982091356</v>
+        <v>34.99223982091359</v>
       </c>
       <c r="G17" t="n">
-        <v>32.60496463124692</v>
+        <v>32.60496463124693</v>
       </c>
       <c r="H17" t="n">
         <v>29.6</v>
@@ -5509,7 +5509,7 @@
         <v>29.6</v>
       </c>
       <c r="K17" t="n">
-        <v>263.7476832091189</v>
+        <v>79.21329778894473</v>
       </c>
       <c r="L17" t="n">
         <v>325.2973662241943</v>
@@ -5542,16 +5542,16 @@
         <v>957.7663257204202</v>
       </c>
       <c r="V17" t="n">
-        <v>726.6036750468608</v>
+        <v>726.9505301014393</v>
       </c>
       <c r="W17" t="n">
-        <v>486.8324871873177</v>
+        <v>487.1793422418963</v>
       </c>
       <c r="X17" t="n">
-        <v>293.618513994724</v>
+        <v>293.9653690493026</v>
       </c>
       <c r="Y17" t="n">
-        <v>182.1867638100711</v>
+        <v>182.5336188646497</v>
       </c>
     </row>
     <row r="18">
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.6</v>
+        <v>394.3473863086054</v>
       </c>
       <c r="C18" t="n">
         <v>29.6</v>
@@ -5591,13 +5591,13 @@
         <v>396.1634226847767</v>
       </c>
       <c r="L18" t="n">
-        <v>712.8249701290334</v>
+        <v>712.4151597604979</v>
       </c>
       <c r="M18" t="n">
-        <v>851.7814118718926</v>
+        <v>851.3716015033571</v>
       </c>
       <c r="N18" t="n">
-        <v>1039.33706421531</v>
+        <v>1038.927253846774</v>
       </c>
       <c r="O18" t="n">
         <v>1327.621063455022</v>
@@ -5615,22 +5615,22 @@
         <v>1135.548898333983</v>
       </c>
       <c r="T18" t="n">
-        <v>827.8180629850668</v>
+        <v>1132.005339032892</v>
       </c>
       <c r="U18" t="n">
-        <v>454.080689247693</v>
+        <v>1132.005339032892</v>
       </c>
       <c r="V18" t="n">
-        <v>80.34331551031926</v>
+        <v>1118.358200455599</v>
       </c>
       <c r="W18" t="n">
-        <v>48.65327216705813</v>
+        <v>1086.668157112338</v>
       </c>
       <c r="X18" t="n">
-        <v>29.6</v>
+        <v>1067.61488494528</v>
       </c>
       <c r="Y18" t="n">
-        <v>29.6</v>
+        <v>693.877511207906</v>
       </c>
     </row>
     <row r="19">
@@ -5640,31 +5640,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>769.4615579355411</v>
+        <v>219.4132103063458</v>
       </c>
       <c r="C19" t="n">
-        <v>896.4535637539769</v>
+        <v>346.4052161247816</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.762707878977</v>
+        <v>412.2449817426217</v>
       </c>
       <c r="E19" t="n">
-        <v>1129.58161209039</v>
+        <v>531.0638859540347</v>
       </c>
       <c r="F19" t="n">
-        <v>1254.932584682326</v>
+        <v>656.4148585459702</v>
       </c>
       <c r="G19" t="n">
-        <v>1254.932584682326</v>
+        <v>656.4148585459702</v>
       </c>
       <c r="H19" t="n">
-        <v>1381.780003550069</v>
+        <v>656.4148585459702</v>
       </c>
       <c r="I19" t="n">
-        <v>1381.780003550069</v>
+        <v>883.799084367299</v>
       </c>
       <c r="J19" t="n">
-        <v>1381.780003550069</v>
+        <v>1250.099084367299</v>
       </c>
       <c r="K19" t="n">
         <v>1381.780003550069</v>
@@ -5685,7 +5685,7 @@
         <v>663.6377390099635</v>
       </c>
       <c r="Q19" t="n">
-        <v>350.4647426204705</v>
+        <v>350.4647426204706</v>
       </c>
       <c r="R19" t="n">
         <v>29.6</v>
@@ -5703,13 +5703,13 @@
         <v>219.4132103063458</v>
       </c>
       <c r="W19" t="n">
-        <v>392.2941285660232</v>
+        <v>219.4132103063458</v>
       </c>
       <c r="X19" t="n">
-        <v>544.3149195902167</v>
+        <v>219.4132103063458</v>
       </c>
       <c r="Y19" t="n">
-        <v>656.714220269249</v>
+        <v>219.4132103063458</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100.3692759761575</v>
+        <v>100.716131030736</v>
       </c>
       <c r="C20" t="n">
-        <v>51.40505552868886</v>
+        <v>51.75191058326739</v>
       </c>
       <c r="D20" t="n">
-        <v>41.97156488237594</v>
+        <v>42.31841993695447</v>
       </c>
       <c r="E20" t="n">
-        <v>38.5743026532157</v>
+        <v>38.92115770779422</v>
       </c>
       <c r="F20" t="n">
-        <v>34.64538476633503</v>
+        <v>34.99223982091356</v>
       </c>
       <c r="G20" t="n">
-        <v>32.60496463124693</v>
+        <v>32.60496463124692</v>
       </c>
       <c r="H20" t="n">
         <v>29.6</v>
@@ -5776,19 +5776,19 @@
         <v>1208.46307214534</v>
       </c>
       <c r="U20" t="n">
-        <v>957.7663257204202</v>
+        <v>958.1131807749988</v>
       </c>
       <c r="V20" t="n">
-        <v>726.6036750468608</v>
+        <v>726.9505301014393</v>
       </c>
       <c r="W20" t="n">
-        <v>486.8324871873177</v>
+        <v>487.1793422418963</v>
       </c>
       <c r="X20" t="n">
-        <v>293.618513994724</v>
+        <v>293.9653690493026</v>
       </c>
       <c r="Y20" t="n">
-        <v>182.1867638100711</v>
+        <v>182.5336188646496</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1091.933026833469</v>
+        <v>691.883857866529</v>
       </c>
       <c r="C21" t="n">
-        <v>727.185640524864</v>
+        <v>691.883857866529</v>
       </c>
       <c r="D21" t="n">
-        <v>375.7334315372855</v>
+        <v>691.883857866529</v>
       </c>
       <c r="E21" t="n">
-        <v>29.6</v>
+        <v>691.883857866529</v>
       </c>
       <c r="F21" t="n">
-        <v>29.6</v>
+        <v>691.883857866529</v>
       </c>
       <c r="G21" t="n">
-        <v>29.6</v>
+        <v>363.066945318855</v>
       </c>
       <c r="H21" t="n">
         <v>29.6</v>
@@ -5828,10 +5828,10 @@
         <v>396.1634226847767</v>
       </c>
       <c r="L21" t="n">
-        <v>712.4151597604979</v>
+        <v>712.8249701290334</v>
       </c>
       <c r="M21" t="n">
-        <v>851.3716015033571</v>
+        <v>851.7814118718926</v>
       </c>
       <c r="N21" t="n">
         <v>1038.927253846774</v>
@@ -5846,28 +5846,28 @@
         <v>1480</v>
       </c>
       <c r="R21" t="n">
-        <v>1345.468510453667</v>
+        <v>1106.262626262626</v>
       </c>
       <c r="S21" t="n">
-        <v>1283.197174487888</v>
+        <v>1043.991290296848</v>
       </c>
       <c r="T21" t="n">
-        <v>1279.653615186798</v>
+        <v>756.2743119541412</v>
       </c>
       <c r="U21" t="n">
-        <v>1279.653615186798</v>
+        <v>756.2743119541412</v>
       </c>
       <c r="V21" t="n">
-        <v>1266.006476609504</v>
+        <v>742.6271733768482</v>
       </c>
       <c r="W21" t="n">
-        <v>1234.316433266243</v>
+        <v>710.9371300335871</v>
       </c>
       <c r="X21" t="n">
-        <v>1215.263161099185</v>
+        <v>691.883857866529</v>
       </c>
       <c r="Y21" t="n">
-        <v>1215.263161099185</v>
+        <v>691.883857866529</v>
       </c>
     </row>
     <row r="22">
@@ -5877,34 +5877,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>972.1055185382471</v>
+        <v>656.0627360105988</v>
       </c>
       <c r="C22" t="n">
-        <v>1099.097524356683</v>
+        <v>783.0547418290346</v>
       </c>
       <c r="D22" t="n">
-        <v>1213.406668481683</v>
+        <v>897.3638859540347</v>
       </c>
       <c r="E22" t="n">
-        <v>1213.406668481683</v>
+        <v>897.3638859540347</v>
       </c>
       <c r="F22" t="n">
-        <v>1213.406668481683</v>
+        <v>1022.71485854597</v>
       </c>
       <c r="G22" t="n">
-        <v>1213.406668481683</v>
+        <v>1022.71485854597</v>
       </c>
       <c r="H22" t="n">
-        <v>1385.468754624687</v>
+        <v>1022.71485854597</v>
       </c>
       <c r="I22" t="n">
-        <v>1385.468754624687</v>
+        <v>1250.099084367299</v>
       </c>
       <c r="J22" t="n">
-        <v>1385.468754624687</v>
+        <v>1250.099084367299</v>
       </c>
       <c r="K22" t="n">
-        <v>1385.468754624687</v>
+        <v>1381.780003550069</v>
       </c>
       <c r="L22" t="n">
         <v>1385.468754624687</v>
@@ -5922,31 +5922,31 @@
         <v>663.6377390099635</v>
       </c>
       <c r="Q22" t="n">
-        <v>350.4647426204706</v>
+        <v>350.4647426204705</v>
       </c>
       <c r="R22" t="n">
         <v>29.6</v>
       </c>
       <c r="S22" t="n">
-        <v>29.6</v>
+        <v>70.88922788105836</v>
       </c>
       <c r="T22" t="n">
-        <v>29.6</v>
+        <v>70.88922788105836</v>
       </c>
       <c r="U22" t="n">
-        <v>277.1507355891063</v>
+        <v>70.88922788105836</v>
       </c>
       <c r="V22" t="n">
-        <v>476.9621284750523</v>
+        <v>106.0143883814035</v>
       </c>
       <c r="W22" t="n">
-        <v>649.8430467347297</v>
+        <v>278.8953066410809</v>
       </c>
       <c r="X22" t="n">
-        <v>801.8638377589232</v>
+        <v>430.9160976652744</v>
       </c>
       <c r="Y22" t="n">
-        <v>859.358180871955</v>
+        <v>543.3153983443067</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100.3692759761575</v>
+        <v>100.716131030736</v>
       </c>
       <c r="C23" t="n">
-        <v>51.40505552868886</v>
+        <v>51.75191058326739</v>
       </c>
       <c r="D23" t="n">
-        <v>41.97156488237594</v>
+        <v>42.31841993695447</v>
       </c>
       <c r="E23" t="n">
-        <v>38.5743026532157</v>
+        <v>38.92115770779422</v>
       </c>
       <c r="F23" t="n">
-        <v>34.64538476633503</v>
+        <v>34.99223982091356</v>
       </c>
       <c r="G23" t="n">
-        <v>32.60496463124693</v>
+        <v>32.60496463124692</v>
       </c>
       <c r="H23" t="n">
         <v>29.6</v>
@@ -5980,52 +5980,52 @@
         <v>29.6</v>
       </c>
       <c r="J23" t="n">
-        <v>395.9</v>
+        <v>29.6</v>
       </c>
       <c r="K23" t="n">
-        <v>445.5132977889448</v>
+        <v>79.21329778894473</v>
       </c>
       <c r="L23" t="n">
-        <v>507.0629808040202</v>
+        <v>325.2973662242488</v>
       </c>
       <c r="M23" t="n">
-        <v>873.3629808040203</v>
+        <v>691.5973662242588</v>
       </c>
       <c r="N23" t="n">
-        <v>1239.66298080402</v>
+        <v>1057.897366224269</v>
       </c>
       <c r="O23" t="n">
-        <v>1239.66298080402</v>
+        <v>1057.897366224269</v>
       </c>
       <c r="P23" t="n">
-        <v>1295.465614579826</v>
+        <v>1113.700000000075</v>
       </c>
       <c r="Q23" t="n">
-        <v>1480</v>
+        <v>1480.000000000085</v>
       </c>
       <c r="R23" t="n">
-        <v>1480</v>
+        <v>1480.000000000085</v>
       </c>
       <c r="S23" t="n">
-        <v>1394.272141552905</v>
+        <v>1394.272141552989</v>
       </c>
       <c r="T23" t="n">
-        <v>1208.46307214534</v>
+        <v>1208.463072145425</v>
       </c>
       <c r="U23" t="n">
-        <v>957.7663257204202</v>
+        <v>957.7663257205048</v>
       </c>
       <c r="V23" t="n">
-        <v>726.6036750468608</v>
+        <v>726.9505301014393</v>
       </c>
       <c r="W23" t="n">
-        <v>486.8324871873177</v>
+        <v>487.1793422418963</v>
       </c>
       <c r="X23" t="n">
-        <v>293.618513994724</v>
+        <v>293.9653690493026</v>
       </c>
       <c r="Y23" t="n">
-        <v>182.1867638100711</v>
+        <v>182.5336188646496</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.6</v>
+        <v>1088.866506748585</v>
       </c>
       <c r="C24" t="n">
-        <v>29.6</v>
+        <v>724.1191204399794</v>
       </c>
       <c r="D24" t="n">
-        <v>29.6</v>
+        <v>372.6669114524009</v>
       </c>
       <c r="E24" t="n">
-        <v>29.6</v>
+        <v>372.6669114524009</v>
       </c>
       <c r="F24" t="n">
         <v>29.6</v>
@@ -6065,46 +6065,46 @@
         <v>396.1634226847767</v>
       </c>
       <c r="L24" t="n">
-        <v>712.4151597604979</v>
+        <v>712.8249701290334</v>
       </c>
       <c r="M24" t="n">
-        <v>851.3716015033571</v>
+        <v>851.7814118718926</v>
       </c>
       <c r="N24" t="n">
-        <v>1038.927253846774</v>
+        <v>1039.33706421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1327.621063455022</v>
+        <v>1327.621063455106</v>
       </c>
       <c r="P24" t="n">
-        <v>1480</v>
+        <v>1480.000000000085</v>
       </c>
       <c r="Q24" t="n">
-        <v>1332.351723846095</v>
+        <v>1480.000000000085</v>
       </c>
       <c r="R24" t="n">
-        <v>1197.820234299761</v>
+        <v>1345.468510453751</v>
       </c>
       <c r="S24" t="n">
-        <v>1135.548898333983</v>
+        <v>1283.197174487973</v>
       </c>
       <c r="T24" t="n">
-        <v>1132.005339032892</v>
+        <v>1279.653615186882</v>
       </c>
       <c r="U24" t="n">
-        <v>1132.005339032892</v>
+        <v>1279.653615186882</v>
       </c>
       <c r="V24" t="n">
-        <v>796.1280196418057</v>
+        <v>1266.006476609589</v>
       </c>
       <c r="W24" t="n">
-        <v>422.3906459044319</v>
+        <v>1234.316433266328</v>
       </c>
       <c r="X24" t="n">
-        <v>403.3373737373738</v>
+        <v>1215.26316109927</v>
       </c>
       <c r="Y24" t="n">
-        <v>29.6</v>
+        <v>1215.26316109927</v>
       </c>
     </row>
     <row r="25">
@@ -6114,25 +6114,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1027.010476104248</v>
+        <v>621.0005114428026</v>
       </c>
       <c r="C25" t="n">
-        <v>1095.527564382053</v>
+        <v>747.9925172612384</v>
       </c>
       <c r="D25" t="n">
-        <v>1095.527564382053</v>
+        <v>862.3016613862385</v>
       </c>
       <c r="E25" t="n">
-        <v>1095.527564382053</v>
+        <v>868.1433385607243</v>
       </c>
       <c r="F25" t="n">
-        <v>1095.527564382053</v>
+        <v>868.1433385607243</v>
       </c>
       <c r="G25" t="n">
-        <v>1250.099084367299</v>
+        <v>1022.71485854597</v>
       </c>
       <c r="H25" t="n">
-        <v>1250.099084367299</v>
+        <v>1022.71485854597</v>
       </c>
       <c r="I25" t="n">
         <v>1250.099084367299</v>
@@ -6159,31 +6159,31 @@
         <v>663.6377390099635</v>
       </c>
       <c r="Q25" t="n">
-        <v>350.4647426204706</v>
+        <v>350.4647426204705</v>
       </c>
       <c r="R25" t="n">
         <v>29.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.6</v>
+        <v>70.88922788105836</v>
       </c>
       <c r="T25" t="n">
-        <v>29.6</v>
+        <v>260.7024381874042</v>
       </c>
       <c r="U25" t="n">
-        <v>277.1507355891063</v>
+        <v>508.2531737765105</v>
       </c>
       <c r="V25" t="n">
-        <v>476.9621284750523</v>
+        <v>508.2531737765105</v>
       </c>
       <c r="W25" t="n">
-        <v>649.8430467347297</v>
+        <v>508.2531737765105</v>
       </c>
       <c r="X25" t="n">
-        <v>801.8638377589232</v>
+        <v>508.2531737765105</v>
       </c>
       <c r="Y25" t="n">
-        <v>914.2631384379555</v>
+        <v>508.2531737765105</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>120.9479077858706</v>
+        <v>358.2196454219982</v>
       </c>
       <c r="C26" t="n">
-        <v>120.9479077858706</v>
+        <v>219.3564350755397</v>
       </c>
       <c r="D26" t="n">
-        <v>120.9479077858706</v>
+        <v>120.0239545302368</v>
       </c>
       <c r="E26" t="n">
-        <v>120.9479077858706</v>
+        <v>120.0239545302368</v>
       </c>
       <c r="F26" t="n">
-        <v>27.12</v>
+        <v>120.0239545302368</v>
       </c>
       <c r="G26" t="n">
-        <v>27.12</v>
+        <v>120.0239545302368</v>
       </c>
       <c r="H26" t="n">
         <v>27.12</v>
@@ -6217,25 +6217,25 @@
         <v>27.12</v>
       </c>
       <c r="J26" t="n">
-        <v>362.73</v>
+        <v>362.7300000000176</v>
       </c>
       <c r="K26" t="n">
-        <v>412.3432977889448</v>
+        <v>412.3432977889624</v>
       </c>
       <c r="L26" t="n">
-        <v>747.9532977889447</v>
+        <v>473.8929808040377</v>
       </c>
       <c r="M26" t="n">
-        <v>964.5873662241942</v>
+        <v>809.5029808040554</v>
       </c>
       <c r="N26" t="n">
-        <v>1300.197366224194</v>
+        <v>964.5873662241765</v>
       </c>
       <c r="O26" t="n">
-        <v>1300.197366224194</v>
+        <v>964.5873662241765</v>
       </c>
       <c r="P26" t="n">
-        <v>1356</v>
+        <v>1020.389999999982</v>
       </c>
       <c r="Q26" t="n">
         <v>1356</v>
@@ -6244,25 +6244,25 @@
         <v>1356</v>
       </c>
       <c r="S26" t="n">
-        <v>1356</v>
+        <v>1180.373151653915</v>
       </c>
       <c r="T26" t="n">
-        <v>1112.275462440863</v>
+        <v>904.6650923473605</v>
       </c>
       <c r="U26" t="n">
-        <v>771.6797261169529</v>
+        <v>731.2668632385445</v>
       </c>
       <c r="V26" t="n">
-        <v>450.6180855444035</v>
+        <v>731.2668632385445</v>
       </c>
       <c r="W26" t="n">
-        <v>120.9479077858706</v>
+        <v>731.2668632385445</v>
       </c>
       <c r="X26" t="n">
-        <v>120.9479077858706</v>
+        <v>731.2668632385445</v>
       </c>
       <c r="Y26" t="n">
-        <v>120.9479077858706</v>
+        <v>529.9361231549017</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>203.8947052433081</v>
+        <v>301.2182709495696</v>
       </c>
       <c r="C27" t="n">
-        <v>154.2988340862179</v>
+        <v>251.6223997924794</v>
       </c>
       <c r="D27" t="n">
-        <v>117.9981402501546</v>
+        <v>215.3217059564162</v>
       </c>
       <c r="E27" t="n">
-        <v>87.01622386438427</v>
+        <v>184.3397895706458</v>
       </c>
       <c r="F27" t="n">
-        <v>59.10082756349856</v>
+        <v>156.4243932697601</v>
       </c>
       <c r="G27" t="n">
-        <v>45.43543016733982</v>
+        <v>142.7589958736014</v>
       </c>
       <c r="H27" t="n">
         <v>27.12</v>
@@ -6311,37 +6311,37 @@
         <v>1036.85706421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1203.621063455022</v>
+        <v>1325.550873823557</v>
       </c>
       <c r="P27" t="n">
         <v>1356</v>
       </c>
       <c r="Q27" t="n">
-        <v>1258.676434293739</v>
+        <v>1356</v>
       </c>
       <c r="R27" t="n">
-        <v>1034.245954848416</v>
+        <v>1131.569520554677</v>
       </c>
       <c r="S27" t="n">
-        <v>882.075628983647</v>
+        <v>979.3991946899085</v>
       </c>
       <c r="T27" t="n">
-        <v>788.6330797835664</v>
+        <v>885.9566454898279</v>
       </c>
       <c r="U27" t="n">
-        <v>699.5457142930022</v>
+        <v>796.8692799992638</v>
       </c>
       <c r="V27" t="n">
-        <v>595.9995858167192</v>
+        <v>693.3231515229808</v>
       </c>
       <c r="W27" t="n">
-        <v>474.4105525744682</v>
+        <v>571.7341182807297</v>
       </c>
       <c r="X27" t="n">
-        <v>365.4582905084201</v>
+        <v>462.7818562146817</v>
       </c>
       <c r="Y27" t="n">
-        <v>277.1841564012137</v>
+        <v>374.5077221074753</v>
       </c>
     </row>
     <row r="28">
@@ -6390,13 +6390,13 @@
         <v>846.8170391837274</v>
       </c>
       <c r="O28" t="n">
-        <v>846.8170391837274</v>
+        <v>540.2849078901372</v>
       </c>
       <c r="P28" t="n">
-        <v>504.392796759485</v>
+        <v>197.8606654658225</v>
       </c>
       <c r="Q28" t="n">
-        <v>161.9685543352425</v>
+        <v>74.89142344550724</v>
       </c>
       <c r="R28" t="n">
         <v>74.89142344550724</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>370.1696413333371</v>
+        <v>81.55948225342405</v>
       </c>
       <c r="C29" t="n">
-        <v>231.3064309868786</v>
+        <v>81.55948225342405</v>
       </c>
       <c r="D29" t="n">
-        <v>131.9739504415758</v>
+        <v>81.55948225342405</v>
       </c>
       <c r="E29" t="n">
-        <v>131.9739504415758</v>
+        <v>27.12</v>
       </c>
       <c r="F29" t="n">
-        <v>38.1460426557052</v>
+        <v>27.12</v>
       </c>
       <c r="G29" t="n">
         <v>27.12</v>
@@ -6454,25 +6454,25 @@
         <v>27.12</v>
       </c>
       <c r="J29" t="n">
-        <v>362.73</v>
+        <v>362.7300000000114</v>
       </c>
       <c r="K29" t="n">
-        <v>698.34</v>
+        <v>412.3432977889562</v>
       </c>
       <c r="L29" t="n">
-        <v>759.8896830150754</v>
+        <v>473.8929808040315</v>
       </c>
       <c r="M29" t="n">
-        <v>964.5873662241942</v>
+        <v>809.5029808040431</v>
       </c>
       <c r="N29" t="n">
-        <v>964.5873662241942</v>
+        <v>964.5873662241827</v>
       </c>
       <c r="O29" t="n">
-        <v>964.5873662241942</v>
+        <v>964.5873662241827</v>
       </c>
       <c r="P29" t="n">
-        <v>1020.39</v>
+        <v>1020.389999999989</v>
       </c>
       <c r="Q29" t="n">
         <v>1356</v>
@@ -6487,19 +6487,19 @@
         <v>1356</v>
       </c>
       <c r="U29" t="n">
-        <v>1356</v>
+        <v>1015.40426367609</v>
       </c>
       <c r="V29" t="n">
-        <v>1356</v>
+        <v>694.3426231035405</v>
       </c>
       <c r="W29" t="n">
-        <v>1026.329822241467</v>
+        <v>364.6724453450076</v>
       </c>
       <c r="X29" t="n">
-        <v>743.2168591498835</v>
+        <v>81.55948225342405</v>
       </c>
       <c r="Y29" t="n">
-        <v>541.8861190662407</v>
+        <v>81.55948225342405</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>301.2182709495697</v>
+        <v>301.2182709495696</v>
       </c>
       <c r="C30" t="n">
-        <v>251.6223997924795</v>
+        <v>251.6223997924794</v>
       </c>
       <c r="D30" t="n">
-        <v>215.3217059564163</v>
+        <v>215.3217059564162</v>
       </c>
       <c r="E30" t="n">
-        <v>184.339789570646</v>
+        <v>184.3397895706458</v>
       </c>
       <c r="F30" t="n">
-        <v>156.4243932697602</v>
+        <v>59.10082756349856</v>
       </c>
       <c r="G30" t="n">
-        <v>142.7589958736015</v>
+        <v>45.43543016733982</v>
       </c>
       <c r="H30" t="n">
-        <v>124.4435657062616</v>
+        <v>27.12</v>
       </c>
       <c r="I30" t="n">
         <v>27.12</v>
@@ -6566,19 +6566,19 @@
         <v>885.9566454898279</v>
       </c>
       <c r="U30" t="n">
-        <v>796.8692799992639</v>
+        <v>796.8692799992638</v>
       </c>
       <c r="V30" t="n">
-        <v>693.3231515229809</v>
+        <v>693.3231515229808</v>
       </c>
       <c r="W30" t="n">
-        <v>571.7341182807298</v>
+        <v>571.7341182807297</v>
       </c>
       <c r="X30" t="n">
-        <v>462.7818562146818</v>
+        <v>462.7818562146817</v>
       </c>
       <c r="Y30" t="n">
-        <v>374.5077221074754</v>
+        <v>374.5077221074753</v>
       </c>
     </row>
     <row r="31">
@@ -6627,22 +6627,22 @@
         <v>1029.57435489089</v>
       </c>
       <c r="O31" t="n">
-        <v>723.0422235972995</v>
+        <v>723.0422235972994</v>
       </c>
       <c r="P31" t="n">
-        <v>417.3156658697496</v>
+        <v>380.6179811730453</v>
       </c>
       <c r="Q31" t="n">
-        <v>417.3156658697496</v>
+        <v>74.89142344550724</v>
       </c>
       <c r="R31" t="n">
-        <v>74.89142344550723</v>
+        <v>74.89142344550724</v>
       </c>
       <c r="S31" t="n">
         <v>27.12</v>
       </c>
       <c r="T31" t="n">
-        <v>128.8232103063458</v>
+        <v>128.8232103063459</v>
       </c>
       <c r="U31" t="n">
         <v>288.2639458954521</v>
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>56.94240226565042</v>
+        <v>56.54240226565042</v>
       </c>
       <c r="C32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="D32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="E32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="F32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="G32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="H32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="I32" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="J32" t="n">
-        <v>349.89</v>
+        <v>25.76</v>
       </c>
       <c r="K32" t="n">
-        <v>399.5032977889448</v>
+        <v>344.54</v>
       </c>
       <c r="L32" t="n">
-        <v>461.0529808040201</v>
+        <v>406.0896830150754</v>
       </c>
       <c r="M32" t="n">
-        <v>784.7829808040202</v>
+        <v>724.8696830150753</v>
       </c>
       <c r="N32" t="n">
-        <v>1108.51298080402</v>
+        <v>1043.649683015075</v>
       </c>
       <c r="O32" t="n">
-        <v>1108.51298080402</v>
+        <v>1043.649683015075</v>
       </c>
       <c r="P32" t="n">
-        <v>1164.315614579826</v>
+        <v>1099.452316790881</v>
       </c>
       <c r="Q32" t="n">
-        <v>1308</v>
+        <v>1288</v>
       </c>
       <c r="R32" t="n">
-        <v>1291.118580834948</v>
+        <v>1288</v>
       </c>
       <c r="S32" t="n">
-        <v>1223.57254056967</v>
+        <v>1223.17254056967</v>
       </c>
       <c r="T32" t="n">
-        <v>1055.945289343924</v>
+        <v>1055.545289343924</v>
       </c>
       <c r="U32" t="n">
-        <v>823.4303611008222</v>
+        <v>823.0303611008222</v>
       </c>
       <c r="V32" t="n">
-        <v>610.4495286090809</v>
+        <v>610.0495286090809</v>
       </c>
       <c r="W32" t="n">
-        <v>388.8601589313561</v>
+        <v>388.4601589313561</v>
       </c>
       <c r="X32" t="n">
-        <v>213.8280039205806</v>
+        <v>213.4280039205806</v>
       </c>
       <c r="Y32" t="n">
-        <v>120.5780719177459</v>
+        <v>120.1780719177459</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26.16</v>
+        <v>563.001251233876</v>
       </c>
       <c r="C33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="D33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="E33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="F33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="G33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="H33" t="n">
-        <v>26.16</v>
+        <v>237.7487259813507</v>
       </c>
       <c r="I33" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="J33" t="n">
-        <v>169.8326316847329</v>
+        <v>169.4326316847329</v>
       </c>
       <c r="K33" t="n">
-        <v>392.7234226847767</v>
+        <v>392.3234226847767</v>
       </c>
       <c r="L33" t="n">
-        <v>692.7940963054763</v>
+        <v>708.9849701290334</v>
       </c>
       <c r="M33" t="n">
-        <v>831.7505380483354</v>
+        <v>847.9414118718926</v>
       </c>
       <c r="N33" t="n">
-        <v>1019.306190391753</v>
+        <v>1035.49706421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1308</v>
+        <v>1135.621063455022</v>
       </c>
       <c r="P33" t="n">
-        <v>1308</v>
+        <v>1288</v>
       </c>
       <c r="Q33" t="n">
-        <v>1308</v>
+        <v>1140.351723846095</v>
       </c>
       <c r="R33" t="n">
-        <v>1191.650328635485</v>
+        <v>946.7229734170445</v>
       </c>
       <c r="S33" t="n">
-        <v>1147.560810851525</v>
+        <v>902.6334556330842</v>
       </c>
       <c r="T33" t="n">
-        <v>1147.560810851525</v>
+        <v>902.6334556330842</v>
       </c>
       <c r="U33" t="n">
-        <v>817.2577805484943</v>
+        <v>902.6334556330842</v>
       </c>
       <c r="V33" t="n">
-        <v>486.954750245464</v>
+        <v>902.6334556330842</v>
       </c>
       <c r="W33" t="n">
-        <v>156.6517199424337</v>
+        <v>889.1252304716412</v>
       </c>
       <c r="X33" t="n">
-        <v>26.16</v>
+        <v>888.2537764864013</v>
       </c>
       <c r="Y33" t="n">
-        <v>26.16</v>
+        <v>888.2537764864013</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="C34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="D34" t="n">
-        <v>558.2731737765105</v>
+        <v>216.9983720060584</v>
       </c>
       <c r="E34" t="n">
-        <v>558.2731737765105</v>
+        <v>353.6372762174715</v>
       </c>
       <c r="F34" t="n">
-        <v>558.2731737765105</v>
+        <v>353.6372762174715</v>
       </c>
       <c r="G34" t="n">
-        <v>558.2731737765105</v>
+        <v>526.0287962027173</v>
       </c>
       <c r="H34" t="n">
-        <v>748.1552599195146</v>
+        <v>537.5439494550611</v>
       </c>
       <c r="I34" t="n">
-        <v>993.3594857408434</v>
+        <v>782.7481752763899</v>
       </c>
       <c r="J34" t="n">
-        <v>1101.92817527639</v>
+        <v>1101.52817527639</v>
       </c>
       <c r="K34" t="n">
-        <v>1251.42909445916</v>
+        <v>1251.02909445916</v>
       </c>
       <c r="L34" t="n">
-        <v>1272.937845533778</v>
+        <v>1272.537845533778</v>
       </c>
       <c r="M34" t="n">
-        <v>1198.261337907424</v>
+        <v>1197.861337907424</v>
       </c>
       <c r="N34" t="n">
-        <v>1071.855383418721</v>
+        <v>1071.455383418721</v>
       </c>
       <c r="O34" t="n">
-        <v>873.4040602059384</v>
+        <v>873.0040602059385</v>
       </c>
       <c r="P34" t="n">
-        <v>623.8341026463271</v>
+        <v>623.4341026463271</v>
       </c>
       <c r="Q34" t="n">
-        <v>328.8429244386523</v>
+        <v>328.4429244386523</v>
       </c>
       <c r="R34" t="n">
-        <v>26.16</v>
+        <v>25.76</v>
       </c>
       <c r="S34" t="n">
-        <v>85.26922788105836</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="T34" t="n">
-        <v>292.9024381874042</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="U34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="V34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="W34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="X34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
       <c r="Y34" t="n">
-        <v>558.2731737765105</v>
+        <v>84.86922788105836</v>
       </c>
     </row>
     <row r="35">
@@ -6928,25 +6928,25 @@
         <v>24.72</v>
       </c>
       <c r="J35" t="n">
-        <v>330.63</v>
+        <v>24.72</v>
       </c>
       <c r="K35" t="n">
+        <v>74.33329778894472</v>
+      </c>
+      <c r="L35" t="n">
         <v>380.2432977889447</v>
       </c>
-      <c r="L35" t="n">
-        <v>441.7929808040201</v>
-      </c>
       <c r="M35" t="n">
-        <v>747.7029808040202</v>
+        <v>568.3773662241722</v>
       </c>
       <c r="N35" t="n">
-        <v>874.2873662241941</v>
+        <v>874.2873662241832</v>
       </c>
       <c r="O35" t="n">
-        <v>874.2873662241941</v>
+        <v>874.2873662241832</v>
       </c>
       <c r="P35" t="n">
-        <v>930.0899999999999</v>
+        <v>930.089999999989</v>
       </c>
       <c r="Q35" t="n">
         <v>1236</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>648.9624242424243</v>
+        <v>620.464915596771</v>
       </c>
       <c r="C36" t="n">
-        <v>648.9624242424243</v>
+        <v>620.464915596771</v>
       </c>
       <c r="D36" t="n">
-        <v>648.9624242424243</v>
+        <v>620.464915596771</v>
       </c>
       <c r="E36" t="n">
-        <v>648.9624242424243</v>
+        <v>336.8412121212234</v>
       </c>
       <c r="F36" t="n">
-        <v>648.9624242424243</v>
+        <v>24.72</v>
       </c>
       <c r="G36" t="n">
-        <v>336.8412121212122</v>
+        <v>24.72</v>
       </c>
       <c r="H36" t="n">
         <v>24.72</v>
@@ -7007,52 +7007,52 @@
         <v>24.72</v>
       </c>
       <c r="J36" t="n">
-        <v>168.3926316847329</v>
+        <v>24.72</v>
       </c>
       <c r="K36" t="n">
-        <v>391.2834226847767</v>
+        <v>247.6107910000438</v>
       </c>
       <c r="L36" t="n">
-        <v>620.7940963054763</v>
+        <v>468.4151597604979</v>
       </c>
       <c r="M36" t="n">
-        <v>759.7505380483354</v>
+        <v>607.3716015033571</v>
       </c>
       <c r="N36" t="n">
-        <v>947.3061903917528</v>
+        <v>794.9272538467744</v>
       </c>
       <c r="O36" t="n">
-        <v>1236</v>
+        <v>1083.621063455022</v>
       </c>
       <c r="P36" t="n">
         <v>1236</v>
       </c>
       <c r="Q36" t="n">
-        <v>1236</v>
+        <v>1088.351723846095</v>
       </c>
       <c r="R36" t="n">
-        <v>923.8787878787879</v>
+        <v>978.0626585421855</v>
       </c>
       <c r="S36" t="n">
-        <v>656.4100433432611</v>
+        <v>940.0337468188312</v>
       </c>
       <c r="T36" t="n">
-        <v>656.4100433432611</v>
+        <v>940.0337468188312</v>
       </c>
       <c r="U36" t="n">
-        <v>656.4100433432611</v>
+        <v>940.0337468188312</v>
       </c>
       <c r="V36" t="n">
-        <v>656.4100433432611</v>
+        <v>940.0337468188312</v>
       </c>
       <c r="W36" t="n">
-        <v>648.9624242424243</v>
+        <v>932.5861277179944</v>
       </c>
       <c r="X36" t="n">
-        <v>648.9624242424243</v>
+        <v>932.5861277179944</v>
       </c>
       <c r="Y36" t="n">
-        <v>648.9624242424243</v>
+        <v>620.464915596771</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>685.3847369196457</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="C37" t="n">
-        <v>685.3847369196457</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="D37" t="n">
-        <v>823.4538810446458</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="E37" t="n">
-        <v>966.0327852560588</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="F37" t="n">
-        <v>1115.143757847994</v>
+        <v>121.0367069631633</v>
       </c>
       <c r="G37" t="n">
-        <v>1235.134209170142</v>
+        <v>299.3682269484092</v>
       </c>
       <c r="H37" t="n">
-        <v>1235.134209170142</v>
+        <v>495.1903130914133</v>
       </c>
       <c r="I37" t="n">
-        <v>1235.134209170142</v>
+        <v>746.3345389127421</v>
       </c>
       <c r="J37" t="n">
-        <v>1235.134209170142</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="K37" t="n">
-        <v>1235.134209170142</v>
+        <v>1207.685458095523</v>
       </c>
       <c r="L37" t="n">
         <v>1235.134209170142</v>
@@ -7101,37 +7101,37 @@
         <v>1046.172959176296</v>
       </c>
       <c r="O37" t="n">
-        <v>853.7822420241203</v>
+        <v>853.7822420241201</v>
       </c>
       <c r="P37" t="n">
-        <v>610.272890525115</v>
+        <v>610.2728905251149</v>
       </c>
       <c r="Q37" t="n">
-        <v>321.3423183780463</v>
+        <v>321.3423183780462</v>
       </c>
       <c r="R37" t="n">
         <v>24.72</v>
       </c>
       <c r="S37" t="n">
-        <v>24.72</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="T37" t="n">
-        <v>238.2932103063458</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="U37" t="n">
-        <v>509.6039458954522</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="V37" t="n">
-        <v>509.6039458954522</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="W37" t="n">
-        <v>509.6039458954522</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="X37" t="n">
-        <v>685.3847369196457</v>
+        <v>89.76922788105836</v>
       </c>
       <c r="Y37" t="n">
-        <v>685.3847369196457</v>
+        <v>89.76922788105836</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>24.72</v>
       </c>
       <c r="J38" t="n">
-        <v>330.63</v>
+        <v>24.72</v>
       </c>
       <c r="K38" t="n">
-        <v>380.2432977889447</v>
+        <v>200.9176832090866</v>
       </c>
       <c r="L38" t="n">
-        <v>441.7929808040201</v>
+        <v>262.4673662241619</v>
       </c>
       <c r="M38" t="n">
-        <v>747.7029808040202</v>
+        <v>568.3773662241726</v>
       </c>
       <c r="N38" t="n">
-        <v>1053.61298080402</v>
+        <v>874.2873662241834</v>
       </c>
       <c r="O38" t="n">
-        <v>1053.61298080402</v>
+        <v>874.2873662241834</v>
       </c>
       <c r="P38" t="n">
-        <v>1109.415614579826</v>
+        <v>930.0899999999892</v>
       </c>
       <c r="Q38" t="n">
         <v>1236</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>336.8412121212122</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="C39" t="n">
-        <v>24.72</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="D39" t="n">
-        <v>24.72</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="E39" t="n">
-        <v>24.72</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="F39" t="n">
-        <v>24.72</v>
+        <v>548.8299381025738</v>
       </c>
       <c r="G39" t="n">
-        <v>24.72</v>
+        <v>236.7087259813507</v>
       </c>
       <c r="H39" t="n">
-        <v>24.72</v>
+        <v>236.7087259813507</v>
       </c>
       <c r="I39" t="n">
         <v>24.72</v>
@@ -7247,16 +7247,16 @@
         <v>168.3926316847329</v>
       </c>
       <c r="K39" t="n">
-        <v>314.8840963054762</v>
+        <v>391.2834226847767</v>
       </c>
       <c r="L39" t="n">
-        <v>620.7940963054763</v>
+        <v>697.1934226847875</v>
       </c>
       <c r="M39" t="n">
-        <v>759.7505380483354</v>
+        <v>836.1498644276467</v>
       </c>
       <c r="N39" t="n">
-        <v>947.3061903917528</v>
+        <v>1023.705516771064</v>
       </c>
       <c r="O39" t="n">
         <v>1236</v>
@@ -7268,28 +7268,28 @@
         <v>1088.351723846095</v>
       </c>
       <c r="R39" t="n">
-        <v>776.2305117248824</v>
+        <v>978.0626585421855</v>
       </c>
       <c r="S39" t="n">
-        <v>464.1092996036703</v>
+        <v>868.3987693246337</v>
       </c>
       <c r="T39" t="n">
-        <v>464.1092996036703</v>
+        <v>868.3987693246337</v>
       </c>
       <c r="U39" t="n">
-        <v>464.1092996036703</v>
+        <v>868.3987693246337</v>
       </c>
       <c r="V39" t="n">
-        <v>344.2888312220491</v>
+        <v>868.3987693246337</v>
       </c>
       <c r="W39" t="n">
-        <v>336.8412121212122</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="X39" t="n">
-        <v>336.8412121212122</v>
+        <v>860.9511502237968</v>
       </c>
       <c r="Y39" t="n">
-        <v>336.8412121212122</v>
+        <v>860.9511502237968</v>
       </c>
     </row>
     <row r="40">
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24.93840533991056</v>
+        <v>445.999446765378</v>
       </c>
       <c r="C41" t="n">
-        <v>24.93840533991056</v>
+        <v>308.1463374290205</v>
       </c>
       <c r="D41" t="n">
-        <v>24.93840533991056</v>
+        <v>209.8239578938187</v>
       </c>
       <c r="E41" t="n">
-        <v>24.93840533991056</v>
+        <v>117.5378067757696</v>
       </c>
       <c r="F41" t="n">
         <v>24.72</v>
@@ -7405,22 +7405,22 @@
         <v>24.72</v>
       </c>
       <c r="K41" t="n">
-        <v>74.33329778894472</v>
+        <v>330.63</v>
       </c>
       <c r="L41" t="n">
-        <v>135.8829808040201</v>
+        <v>636.54</v>
       </c>
       <c r="M41" t="n">
-        <v>262.467366224194</v>
+        <v>636.5400000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>568.377366224194</v>
+        <v>942.450000000011</v>
       </c>
       <c r="O41" t="n">
-        <v>874.2873662241941</v>
+        <v>942.450000000011</v>
       </c>
       <c r="P41" t="n">
-        <v>930.0899999999999</v>
+        <v>998.2526337758168</v>
       </c>
       <c r="Q41" t="n">
         <v>1236</v>
@@ -7432,22 +7432,22 @@
         <v>1236</v>
       </c>
       <c r="T41" t="n">
-        <v>961.3020417035469</v>
+        <v>1236</v>
       </c>
       <c r="U41" t="n">
-        <v>649.1808295823348</v>
+        <v>923.878787878746</v>
       </c>
       <c r="V41" t="n">
-        <v>337.0596174611227</v>
+        <v>923.878787878746</v>
       </c>
       <c r="W41" t="n">
-        <v>24.93840533991056</v>
+        <v>611.7575757574975</v>
       </c>
       <c r="X41" t="n">
-        <v>24.93840533991056</v>
+        <v>611.7575757574975</v>
       </c>
       <c r="Y41" t="n">
-        <v>24.93840533991056</v>
+        <v>611.7575757574975</v>
       </c>
     </row>
     <row r="42">
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>190.3091800404787</v>
+        <v>195.434099182702</v>
       </c>
       <c r="C42" t="n">
-        <v>141.7234098934895</v>
+        <v>146.8483290357128</v>
       </c>
       <c r="D42" t="n">
-        <v>106.4328170675272</v>
+        <v>111.5577362097506</v>
       </c>
       <c r="E42" t="n">
-        <v>76.4610016918579</v>
+        <v>81.58592083408124</v>
       </c>
       <c r="F42" t="n">
-        <v>49.55570640107319</v>
+        <v>54.68062554329653</v>
       </c>
       <c r="G42" t="n">
         <v>42.0253291572388</v>
@@ -7484,19 +7484,19 @@
         <v>168.3926316847329</v>
       </c>
       <c r="K42" t="n">
-        <v>168.3926316847329</v>
+        <v>391.2834226847767</v>
       </c>
       <c r="L42" t="n">
-        <v>468.4151597604979</v>
+        <v>620.7940963054763</v>
       </c>
       <c r="M42" t="n">
-        <v>607.3716015033571</v>
+        <v>759.7505380483354</v>
       </c>
       <c r="N42" t="n">
-        <v>794.9272538467744</v>
+        <v>947.3061903917528</v>
       </c>
       <c r="O42" t="n">
-        <v>1083.621063455022</v>
+        <v>1236</v>
       </c>
       <c r="P42" t="n">
         <v>1236</v>
@@ -7508,25 +7508,25 @@
         <v>1012.579621564778</v>
       </c>
       <c r="S42" t="n">
-        <v>861.4193967101105</v>
+        <v>866.544315852334</v>
       </c>
       <c r="T42" t="n">
-        <v>768.9869485201309</v>
+        <v>774.1118676623543</v>
       </c>
       <c r="U42" t="n">
-        <v>680.9096840396678</v>
+        <v>686.0346031818912</v>
       </c>
       <c r="V42" t="n">
-        <v>578.3736565734858</v>
+        <v>583.4985757157092</v>
       </c>
       <c r="W42" t="n">
-        <v>457.7947243413358</v>
+        <v>462.9196434835592</v>
       </c>
       <c r="X42" t="n">
-        <v>349.8525632853888</v>
+        <v>354.9774824276121</v>
       </c>
       <c r="Y42" t="n">
-        <v>262.5885301882834</v>
+        <v>267.7134493305067</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>474.4672267143171</v>
+        <v>537.2028953863999</v>
       </c>
       <c r="C43" t="n">
-        <v>514.3392325327528</v>
+        <v>577.0749012048357</v>
       </c>
       <c r="D43" t="n">
-        <v>541.5283766577529</v>
+        <v>604.2640453298358</v>
       </c>
       <c r="E43" t="n">
-        <v>573.227280869166</v>
+        <v>635.9629495412488</v>
       </c>
       <c r="F43" t="n">
-        <v>611.4582534611014</v>
+        <v>674.1939221331843</v>
       </c>
       <c r="G43" t="n">
-        <v>678.9097734463473</v>
+        <v>741.6454421184302</v>
       </c>
       <c r="H43" t="n">
-        <v>763.8518595893515</v>
+        <v>826.5875282614343</v>
       </c>
       <c r="I43" t="n">
-        <v>904.1160854106803</v>
+        <v>966.8517540827631</v>
       </c>
       <c r="J43" t="n">
         <v>1191.43908081723</v>
@@ -7566,46 +7566,46 @@
         <v>1236</v>
       </c>
       <c r="L43" t="n">
-        <v>1236</v>
+        <v>1150.874758774225</v>
       </c>
       <c r="M43" t="n">
-        <v>1236</v>
+        <v>969.127544077164</v>
       </c>
       <c r="N43" t="n">
-        <v>1236</v>
+        <v>735.6508825177539</v>
       </c>
       <c r="O43" t="n">
-        <v>961.0836363636364</v>
+        <v>430.1288522342646</v>
       </c>
       <c r="P43" t="n">
-        <v>648.9624242424243</v>
+        <v>383.6025345567185</v>
       </c>
       <c r="Q43" t="n">
-        <v>336.8412121212122</v>
+        <v>383.6025345567185</v>
       </c>
       <c r="R43" t="n">
-        <v>24.72</v>
+        <v>71.48132243540623</v>
       </c>
       <c r="S43" t="n">
         <v>24.72</v>
       </c>
       <c r="T43" t="n">
-        <v>24.72</v>
+        <v>127.4132103063458</v>
       </c>
       <c r="U43" t="n">
-        <v>160.2074861991758</v>
+        <v>287.8439458954522</v>
       </c>
       <c r="V43" t="n">
-        <v>272.8988790851217</v>
+        <v>400.5353387813981</v>
       </c>
       <c r="W43" t="n">
-        <v>358.6597973447991</v>
+        <v>486.2962570410755</v>
       </c>
       <c r="X43" t="n">
-        <v>423.5605883689927</v>
+        <v>486.2962570410755</v>
       </c>
       <c r="Y43" t="n">
-        <v>448.8398890480249</v>
+        <v>511.5755577201078</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>558.2068066410575</v>
+        <v>411.7582697418219</v>
       </c>
       <c r="C44" t="n">
-        <v>392.0708690218717</v>
+        <v>244.6122311125351</v>
       </c>
       <c r="D44" t="n">
-        <v>265.4656612038415</v>
+        <v>116.996922284404</v>
       </c>
       <c r="E44" t="n">
-        <v>144.8966818029641</v>
+        <v>116.996922284404</v>
       </c>
       <c r="F44" t="n">
-        <v>144.8966818029641</v>
+        <v>116.996922284404</v>
       </c>
       <c r="G44" t="n">
-        <v>144.8966818029641</v>
+        <v>24.72</v>
       </c>
       <c r="H44" t="n">
         <v>24.72</v>
@@ -7639,25 +7639,25 @@
         <v>24.72</v>
       </c>
       <c r="J44" t="n">
-        <v>330.63</v>
+        <v>330.6300000000109</v>
       </c>
       <c r="K44" t="n">
-        <v>380.2432977889447</v>
+        <v>380.2432977889557</v>
       </c>
       <c r="L44" t="n">
-        <v>441.7929808040201</v>
+        <v>441.7929808040311</v>
       </c>
       <c r="M44" t="n">
-        <v>747.7029808040202</v>
+        <v>747.702980804042</v>
       </c>
       <c r="N44" t="n">
-        <v>874.2873662241941</v>
+        <v>747.702980804042</v>
       </c>
       <c r="O44" t="n">
-        <v>874.2873662241941</v>
+        <v>1053.612980804053</v>
       </c>
       <c r="P44" t="n">
-        <v>930.0899999999999</v>
+        <v>1109.415614579859</v>
       </c>
       <c r="Q44" t="n">
         <v>1236</v>
@@ -7666,25 +7666,25 @@
         <v>1236</v>
       </c>
       <c r="S44" t="n">
-        <v>1033.100424381187</v>
+        <v>1236</v>
       </c>
       <c r="T44" t="n">
-        <v>1033.100424381187</v>
+        <v>1236</v>
       </c>
       <c r="U44" t="n">
-        <v>720.9792122599753</v>
+        <v>923.8787878787768</v>
       </c>
       <c r="V44" t="n">
-        <v>558.2068066410575</v>
+        <v>923.8787878787768</v>
       </c>
       <c r="W44" t="n">
-        <v>558.2068066410575</v>
+        <v>611.7575757575537</v>
       </c>
       <c r="X44" t="n">
-        <v>558.2068066410575</v>
+        <v>611.7575757575537</v>
       </c>
       <c r="Y44" t="n">
-        <v>558.2068066410575</v>
+        <v>611.7575757575537</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>365.1310688796717</v>
+        <v>329.2434492612908</v>
       </c>
       <c r="C45" t="n">
-        <v>288.2624704498542</v>
+        <v>251.3647498213723</v>
       </c>
       <c r="D45" t="n">
-        <v>224.6890493410637</v>
+        <v>186.7812277024807</v>
       </c>
       <c r="E45" t="n">
-        <v>166.4344056825661</v>
+        <v>127.5164830338821</v>
       </c>
       <c r="F45" t="n">
-        <v>111.2462821089531</v>
+        <v>71.31825845016812</v>
       </c>
       <c r="G45" t="n">
-        <v>70.30815744006708</v>
+        <v>71.31825845016812</v>
       </c>
       <c r="H45" t="n">
         <v>24.72</v>
@@ -7718,10 +7718,10 @@
         <v>24.72</v>
       </c>
       <c r="J45" t="n">
-        <v>24.72</v>
+        <v>168.3926316847329</v>
       </c>
       <c r="K45" t="n">
-        <v>162.5051597604979</v>
+        <v>168.3926316847329</v>
       </c>
       <c r="L45" t="n">
         <v>468.4151597604979</v>
@@ -7742,28 +7742,28 @@
         <v>1236</v>
       </c>
       <c r="R45" t="n">
-        <v>1236</v>
+        <v>1055.532309456348</v>
       </c>
       <c r="S45" t="n">
-        <v>1234.221083529102</v>
+        <v>1055.532309456348</v>
       </c>
       <c r="T45" t="n">
-        <v>1113.505807056294</v>
+        <v>933.8069319734393</v>
       </c>
       <c r="U45" t="n">
-        <v>997.1457142930022</v>
+        <v>816.436738200047</v>
       </c>
       <c r="V45" t="n">
-        <v>866.326858543992</v>
+        <v>684.6077814409357</v>
       </c>
       <c r="W45" t="n">
-        <v>717.4650980290137</v>
+        <v>684.6077814409357</v>
       </c>
       <c r="X45" t="n">
-        <v>581.2401086902383</v>
+        <v>547.3726910920594</v>
       </c>
       <c r="Y45" t="n">
-        <v>465.6932473103047</v>
+        <v>430.8157287020247</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>410.4618962096341</v>
+        <v>407.6470480652691</v>
       </c>
       <c r="C46" t="n">
-        <v>422.6139020280699</v>
+        <v>418.8090538837048</v>
       </c>
       <c r="D46" t="n">
-        <v>422.0722676285189</v>
+        <v>418.8090538837048</v>
       </c>
       <c r="E46" t="n">
-        <v>426.0511718399319</v>
+        <v>421.7979580951178</v>
       </c>
       <c r="F46" t="n">
-        <v>436.5621444318674</v>
+        <v>431.3189306870534</v>
       </c>
       <c r="G46" t="n">
-        <v>476.2936644171133</v>
+        <v>470.0604506722993</v>
       </c>
       <c r="H46" t="n">
-        <v>533.5157505601175</v>
+        <v>526.2925368153034</v>
       </c>
       <c r="I46" t="n">
-        <v>646.0599763814463</v>
+        <v>637.8467626366322</v>
       </c>
       <c r="J46" t="n">
-        <v>905.662971787996</v>
+        <v>896.4597580431819</v>
       </c>
       <c r="K46" t="n">
-        <v>922.503890970766</v>
+        <v>912.3106772259518</v>
       </c>
       <c r="L46" t="n">
-        <v>809.095821462163</v>
+        <v>797.8925067072479</v>
       </c>
       <c r="M46" t="n">
-        <v>599.0657784822732</v>
+        <v>586.8523627172572</v>
       </c>
       <c r="N46" t="n">
-        <v>337.3062886400348</v>
+        <v>324.0827718649177</v>
       </c>
       <c r="O46" t="n">
-        <v>99.7641507182345</v>
+        <v>324.0827718649177</v>
       </c>
       <c r="P46" t="n">
-        <v>99.7641507182345</v>
+        <v>324.0827718649177</v>
       </c>
       <c r="Q46" t="n">
-        <v>99.7641507182345</v>
+        <v>24.72</v>
       </c>
       <c r="R46" t="n">
-        <v>99.7641507182345</v>
+        <v>24.72</v>
       </c>
       <c r="S46" t="n">
         <v>24.72</v>
       </c>
       <c r="T46" t="n">
-        <v>99.69321030634585</v>
+        <v>98.70321030634584</v>
       </c>
       <c r="U46" t="n">
-        <v>232.4039458954522</v>
+        <v>230.4239458954522</v>
       </c>
       <c r="V46" t="n">
-        <v>317.3753387813982</v>
+        <v>314.4053387813981</v>
       </c>
       <c r="W46" t="n">
-        <v>375.4162570410756</v>
+        <v>371.4562570410756</v>
       </c>
       <c r="X46" t="n">
-        <v>412.5970480652691</v>
+        <v>407.6470480652691</v>
       </c>
       <c r="Y46" t="n">
-        <v>412.5970480652691</v>
+        <v>407.6470480652691</v>
       </c>
     </row>
   </sheetData>
@@ -7967,10 +7967,10 @@
         <v>1.605307752628015</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>157.6104903234081</v>
       </c>
       <c r="L2" t="n">
-        <v>157.6104903234081</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>815.08446935086</v>
@@ -8046,7 +8046,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
-        <v>176.6784122079271</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
         <v>388.0893364597981</v>
@@ -8058,7 +8058,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O3" t="n">
-        <v>382.6817988009037</v>
+        <v>263.4799701458174</v>
       </c>
       <c r="P3" t="n">
         <v>219.1507118405495</v>
@@ -8280,13 +8280,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>227.4647419277884</v>
+        <v>108.262913272702</v>
       </c>
       <c r="K6" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
-        <v>268.8875078047117</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M6" t="n">
         <v>471.6948204301074</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>353.6053077526288</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>306.8855577889447</v>
       </c>
       <c r="L8" t="n">
-        <v>289.8286030150754</v>
+        <v>294.8286030150754</v>
       </c>
       <c r="M8" t="n">
-        <v>827.0844693508608</v>
+        <v>832.0844693508669</v>
       </c>
       <c r="N8" t="n">
-        <v>638.2489717676897</v>
+        <v>406.9519329442071</v>
       </c>
       <c r="O8" t="n">
         <v>3.868382136906519</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>130.2783727696965</v>
+        <v>416.4878336022089</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8517,13 +8517,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>227.4647419277884</v>
+        <v>175.5760445858334</v>
       </c>
       <c r="K9" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L9" t="n">
-        <v>316.4026593198632</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M9" t="n">
         <v>471.6948204301074</v>
@@ -8766,10 +8766,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N12" t="n">
-        <v>484.9945773041427</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O12" t="n">
-        <v>382.6817988009037</v>
+        <v>382.2678489337514</v>
       </c>
       <c r="P12" t="n">
         <v>219.1507118405495</v>
@@ -8912,25 +8912,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>1.605307752628015</v>
+        <v>371.6053077526281</v>
       </c>
       <c r="K14" t="n">
-        <v>186.398369111287</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>845.08446935086</v>
+        <v>475.08446935086</v>
       </c>
       <c r="N14" t="n">
-        <v>776.9519329442071</v>
+        <v>649.7165987987322</v>
       </c>
       <c r="O14" t="n">
         <v>3.868382136906519</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>313.6337032567618</v>
       </c>
       <c r="Q14" t="n">
         <v>500.2783727696964</v>
@@ -9152,10 +9152,10 @@
         <v>1.605307752628015</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>186.398369111287</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>845.08446935086</v>
@@ -9234,7 +9234,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L18" t="n">
-        <v>388.0893364597981</v>
+        <v>387.6753865925905</v>
       </c>
       <c r="M18" t="n">
         <v>471.6948204301074</v>
@@ -9243,7 +9243,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>382.2678489336961</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P18" t="n">
         <v>219.1507118405495</v>
@@ -9471,13 +9471,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
-        <v>387.6753865925905</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M21" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N21" t="n">
-        <v>485.4085271713503</v>
+        <v>484.9945773041427</v>
       </c>
       <c r="O21" t="n">
         <v>382.6817988009037</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>371.6053077526281</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>186.3983691113422</v>
       </c>
       <c r="M23" t="n">
-        <v>845.08446935086</v>
+        <v>845.0844693508701</v>
       </c>
       <c r="N23" t="n">
-        <v>776.9519329442071</v>
+        <v>776.9519329442172</v>
       </c>
       <c r="O23" t="n">
         <v>3.868382136906519</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>316.6767418809833</v>
+        <v>500.2783727697066</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9708,7 +9708,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L24" t="n">
-        <v>387.6753865925905</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M24" t="n">
         <v>471.6948204301074</v>
@@ -9717,7 +9717,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.6817988009037</v>
+        <v>382.2678489337815</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>340.6053077526281</v>
+        <v>340.6053077526458</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>276.8286030150754</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>693.9067606995968</v>
+        <v>814.0844693508778</v>
       </c>
       <c r="N26" t="n">
-        <v>745.9519329442071</v>
+        <v>563.6028273079659</v>
       </c>
       <c r="O26" t="n">
         <v>3.868382136906519</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>130.2783727696965</v>
+        <v>469.2783727697143</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9954,10 +9954,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O27" t="n">
-        <v>259.5203741862213</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P27" t="n">
-        <v>219.1507118405495</v>
+        <v>95.98928722586713</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>340.6053077526281</v>
+        <v>340.6053077526395</v>
       </c>
       <c r="K29" t="n">
-        <v>288.8855577889448</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>681.8498059257274</v>
+        <v>814.0844693508715</v>
       </c>
       <c r="N29" t="n">
-        <v>406.9519329442071</v>
+        <v>563.6028273079845</v>
       </c>
       <c r="O29" t="n">
         <v>3.868382136906519</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>469.2783727696964</v>
+        <v>469.278372769708</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>328.6053077526281</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>271.8855577889447</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>802.08446935086</v>
+        <v>797.08446935086</v>
       </c>
       <c r="N32" t="n">
-        <v>733.9519329442071</v>
+        <v>728.9519329442071</v>
       </c>
       <c r="O32" t="n">
         <v>3.868382136906519</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>275.4141156183571</v>
+        <v>320.7305780314326</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10419,7 +10419,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L33" t="n">
-        <v>371.3308780521646</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
@@ -10428,10 +10428,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
-        <v>382.6817988009037</v>
+        <v>192.2072428730901</v>
       </c>
       <c r="P33" t="n">
-        <v>65.23259411834908</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>310.6053077526281</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>246.8286030150754</v>
       </c>
       <c r="M35" t="n">
-        <v>784.08446935086</v>
+        <v>665.1188819116959</v>
       </c>
       <c r="N35" t="n">
-        <v>534.8149485201404</v>
+        <v>715.9519329442182</v>
       </c>
       <c r="O35" t="n">
         <v>3.868382136906519</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>439.2783727696964</v>
+        <v>439.2783727697076</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,13 +10650,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>82.34087153916931</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>300.0581507794373</v>
+        <v>291.263903445856</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10668,7 +10668,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
-        <v>65.23259411834908</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>310.6053077526281</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>127.8630155759009</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>784.08446935086</v>
+        <v>784.0844693508708</v>
       </c>
       <c r="N38" t="n">
-        <v>715.9519329442071</v>
+        <v>715.9519329442179</v>
       </c>
       <c r="O38" t="n">
         <v>3.868382136906519</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>258.1413883456297</v>
+        <v>439.2783727697072</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10890,10 +10890,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
-        <v>218.7092041162454</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>377.2291875262055</v>
+        <v>377.2291875262163</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,7 +10902,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>382.6817988009037</v>
+        <v>305.5107620541247</v>
       </c>
       <c r="P39" t="n">
         <v>65.23259411834908</v>
@@ -11048,25 +11048,25 @@
         <v>1.605307752628015</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>258.8855577889447</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>246.8286030150754</v>
       </c>
       <c r="M41" t="n">
-        <v>602.9474849267932</v>
+        <v>475.08446935086</v>
       </c>
       <c r="N41" t="n">
-        <v>715.9519329442071</v>
+        <v>715.951932944218</v>
       </c>
       <c r="O41" t="n">
-        <v>312.8683821369065</v>
+        <v>3.868382136906519</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>439.2783727696964</v>
+        <v>370.4272275415987</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,10 +11127,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>70.73802773165616</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>371.2822461885943</v>
+        <v>300.0581507794373</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11142,7 +11142,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>65.23259411834908</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>310.6053077526281</v>
+        <v>310.605307752639</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>784.08446935086</v>
+        <v>784.084469350871</v>
       </c>
       <c r="N44" t="n">
-        <v>534.8149485201404</v>
+        <v>406.9519329442071</v>
       </c>
       <c r="O44" t="n">
-        <v>3.868382136906519</v>
+        <v>312.8683821369175</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>439.2783727696964</v>
+        <v>258.1413883455969</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>82.34087153916931</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>209.9149567826641</v>
+        <v>70.73802773165616</v>
       </c>
       <c r="L45" t="n">
-        <v>377.2291875262055</v>
+        <v>371.2822461885943</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.4290690813279</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22581,7 +22581,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>64.17615076644779</v>
       </c>
     </row>
     <row r="3">
@@ -22712,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.838067078440133</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -22749,7 +22749,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>64.17615076644779</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>64.17615076644779</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.6065507664478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -23223,25 +23223,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>123.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>52.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>46.36328960686865</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>46.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>45.36340243776998</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6.200584510527251</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>126.8705798626244</v>
+        <v>127.8705798626244</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23283,16 +23283,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>270.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>190.6217824745842</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>153.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23411,13 +23411,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>38.27398881351688</v>
+        <v>39.27398881351688</v>
       </c>
       <c r="M13" t="n">
-        <v>133.9297425500909</v>
+        <v>134.9297425500909</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>30.77803373940139</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23429,7 +23429,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>24.77803373940145</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>75.27673420630859</v>
+        <v>41.93841678360417</v>
       </c>
       <c r="C14" t="n">
         <v>62.47457824299391</v>
@@ -23475,10 +23475,10 @@
         <v>17.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>16.36340243776998</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>16.97491498493444</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23648,10 +23648,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6880558919572515</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.6880558919573474</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23697,7 +23697,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3433865040327362</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -23757,7 +23757,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3433865040327646</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3433865040327673</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.3433865040327362</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3433865040327673</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3433865039490342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>169.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>137.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>98.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>92.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>92.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>91.36340243776998</v>
       </c>
       <c r="H26" t="n">
-        <v>91.97491498493444</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,25 +24459,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>173.8705798626244</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>31.66368652994295</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>165.5255321429431</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>317.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>326.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>280.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>199.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24605,16 +24605,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>303.4668099806543</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>15.07425798401518</v>
+        <v>15.07425798394365</v>
       </c>
       <c r="Q28" t="n">
-        <v>60.041266425598</v>
+        <v>277.3017168254859</v>
       </c>
       <c r="R28" t="n">
-        <v>320.4497356134279</v>
+        <v>406.6560951942658</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24645,25 +24645,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>169.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>137.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>98.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>92.36328960686865</v>
+        <v>38.46820217597885</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>92.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>80.44762020862184</v>
+        <v>91.36340243776998</v>
       </c>
       <c r="H29" t="n">
-        <v>91.97491498493446</v>
+        <v>91.97491498493444</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,13 +24699,13 @@
         <v>173.8705798626244</v>
       </c>
       <c r="T29" t="n">
-        <v>272.9509787134886</v>
+        <v>272.9509787134885</v>
       </c>
       <c r="U29" t="n">
-        <v>337.189778960671</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>317.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>199.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24845,13 +24845,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>51.40496583374079</v>
+        <v>15.07425798400364</v>
       </c>
       <c r="Q31" t="n">
-        <v>399.041266425598</v>
+        <v>96.37197427533528</v>
       </c>
       <c r="R31" t="n">
-        <v>67.65609519426579</v>
+        <v>406.6560951942658</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.691395026597931</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25593,19 +25593,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>168.9993129555745</v>
+        <v>4.898765253376183</v>
       </c>
       <c r="C41" t="n">
-        <v>136.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>97.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>91.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>91.6734074215004</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>90.36340243776998</v>
@@ -25647,16 +25647,16 @@
         <v>172.8705798626244</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>271.9509787134885</v>
       </c>
       <c r="U41" t="n">
-        <v>27.18977896067097</v>
+        <v>27.18977896062961</v>
       </c>
       <c r="V41" t="n">
-        <v>7.85102416682389</v>
+        <v>316.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>16.37347598094755</v>
+        <v>16.37347598091151</v>
       </c>
       <c r="X41" t="n">
         <v>279.2818334606677</v>
@@ -25687,7 +25687,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>5.073669950801111</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25723,7 +25723,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>5.073669950801275</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25781,28 +25781,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>84.27398881351688</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>179.9297425500909</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>231.1418949438161</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>30.29960998065431</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>44.07425798401518</v>
+        <v>307.0132034832445</v>
       </c>
       <c r="Q43" t="n">
-        <v>89.041266425598</v>
+        <v>398.041266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>96.65609519426582</v>
+        <v>96.65609519416671</v>
       </c>
       <c r="S43" t="n">
-        <v>46.29370921105216</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>196.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25839,16 +25839,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>120.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>119.8896287080119</v>
+        <v>120.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>118.36340243777</v>
+        <v>28.00924937621005</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>119.9749149849345</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>201.8705798626244</v>
       </c>
       <c r="T44" t="n">
-        <v>299.9509787134885</v>
+        <v>300.9509787134886</v>
       </c>
       <c r="U44" t="n">
-        <v>55.18977896067097</v>
+        <v>56.18977896065996</v>
       </c>
       <c r="V44" t="n">
-        <v>183.7063426040953</v>
+        <v>345.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>353.3734759809475</v>
+        <v>45.37347598093658</v>
       </c>
       <c r="X44" t="n">
-        <v>307.2818334606677</v>
+        <v>308.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>226.3174326828064</v>
+        <v>227.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25924,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>41.52874342219718</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>249.1861746508699</v>
+        <v>71.52316101265455</v>
       </c>
       <c r="S45" t="n">
-        <v>175.8874952999313</v>
+        <v>178.6486226061207</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>148.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>3.113800337078658</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1.53621805555548</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -26027,19 +26027,19 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>95.30009343807205</v>
+        <v>331.4668099806543</v>
       </c>
       <c r="P46" t="n">
-        <v>381.0742579840152</v>
+        <v>382.0742579840152</v>
       </c>
       <c r="Q46" t="n">
-        <v>426.041266425598</v>
+        <v>130.6721222793295</v>
       </c>
       <c r="R46" t="n">
-        <v>433.6560951942658</v>
+        <v>434.6560951942658</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>75.29370921105215</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26057,7 +26057,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.465352849462363</v>
+        <v>3.465352849462363</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>924015.5610738466</v>
+        <v>924647.9647661885</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1707933.447781087</v>
+        <v>1708565.851473429</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2496776.75390651</v>
+        <v>2499371.992590392</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3255575.466886535</v>
+        <v>3256267.296479509</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4032907.712777452</v>
+        <v>4033599.542370425</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4820001.279506748</v>
+        <v>4820693.10909972</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5607094.846236041</v>
+        <v>5607786.675829013</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6394188.412965334</v>
+        <v>6394880.242558314</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7096083.998480935</v>
+        <v>7096775.82807391</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7804718.420360172</v>
+        <v>7805410.249953148</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8589220.488749862</v>
+        <v>8588691.512349356</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9372418.266230466</v>
+        <v>9372976.198920868</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10159528.91643834</v>
+        <v>10160086.84912875</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10861393.11463741</v>
+        <v>10861951.04732781</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11524572.91532464</v>
+        <v>11523680.72851504</v>
       </c>
     </row>
   </sheetData>
@@ -26269,49 +26269,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1409913.869426819</v>
+        <v>1411052.196073034</v>
       </c>
       <c r="C2" t="n">
         <v>1411052.196073034</v>
       </c>
       <c r="D2" t="n">
-        <v>1415222.503753034</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="E2" t="n">
-        <v>1358794.512454952</v>
+        <v>1357324.812454952</v>
       </c>
       <c r="F2" t="n">
         <v>1399198.04260365</v>
       </c>
       <c r="G2" t="n">
+        <v>1416768.420112733</v>
+      </c>
+      <c r="H2" t="n">
         <v>1416768.420112734</v>
       </c>
-      <c r="H2" t="n">
-        <v>1416768.420112733</v>
-      </c>
       <c r="I2" t="n">
-        <v>1416768.420112733</v>
+        <v>1416768.42011274</v>
       </c>
       <c r="J2" t="n">
         <v>1275541.959382633</v>
       </c>
       <c r="K2" t="n">
-        <v>1275541.959382634</v>
+        <v>1275541.959382633</v>
       </c>
       <c r="L2" t="n">
+        <v>1416558.155949537</v>
+      </c>
+      <c r="M2" t="n">
         <v>1416799.17037417</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1416799.170374169</v>
       </c>
       <c r="N2" t="n">
         <v>1416799.170374169</v>
       </c>
       <c r="O2" t="n">
-        <v>1263355.556758299</v>
+        <v>1263355.556758298</v>
       </c>
       <c r="P2" t="n">
-        <v>1193723.641237012</v>
+        <v>1191113.426137012</v>
       </c>
     </row>
     <row r="3">
@@ -26321,46 +26321,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>218430</v>
+        <v>219230</v>
       </c>
       <c r="C3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4224</v>
+        <v>5984</v>
       </c>
       <c r="E3" t="n">
-        <v>289536</v>
+        <v>286976</v>
       </c>
       <c r="F3" t="n">
-        <v>22400</v>
+        <v>23200</v>
       </c>
       <c r="G3" t="n">
-        <v>14400</v>
+        <v>15200</v>
       </c>
       <c r="H3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>320768</v>
+        <v>319968</v>
       </c>
       <c r="K3" t="n">
-        <v>22400</v>
+        <v>23200</v>
       </c>
       <c r="L3" t="n">
-        <v>100000</v>
+        <v>100800</v>
       </c>
       <c r="M3" t="n">
-        <v>5600</v>
+        <v>4800</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>122400</v>
+        <v>121600</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>651216.9397313524</v>
+        <v>651781.8831196837</v>
       </c>
       <c r="C4" t="n">
-        <v>649761.3922393249</v>
+        <v>649746.9835658516</v>
       </c>
       <c r="D4" t="n">
-        <v>649281.8321793056</v>
+        <v>649834.9380406409</v>
       </c>
       <c r="E4" t="n">
-        <v>618088.2922080441</v>
+        <v>617333.7551135118</v>
       </c>
       <c r="F4" t="n">
-        <v>636430.5222194825</v>
+        <v>636415.4458457534</v>
       </c>
       <c r="G4" t="n">
-        <v>643180.643022588</v>
+        <v>643165.5666488588</v>
       </c>
       <c r="H4" t="n">
-        <v>641152.8235864354</v>
+        <v>641137.7472127064</v>
       </c>
       <c r="I4" t="n">
-        <v>639122.1732814368</v>
+        <v>639107.0969077104</v>
       </c>
       <c r="J4" t="n">
-        <v>568688.4647812571</v>
+        <v>568674.0783644589</v>
       </c>
       <c r="K4" t="n">
-        <v>566909.6951240613</v>
+        <v>566895.3087072631</v>
       </c>
       <c r="L4" t="n">
-        <v>634584.1570660044</v>
+        <v>634637.1277992827</v>
       </c>
       <c r="M4" t="n">
-        <v>633128.9769891049</v>
+        <v>633115.2582725625</v>
       </c>
       <c r="N4" t="n">
-        <v>631016.5683353457</v>
+        <v>631002.8496188034</v>
       </c>
       <c r="O4" t="n">
-        <v>554865.0720165286</v>
+        <v>554851.3532999863</v>
       </c>
       <c r="P4" t="n">
-        <v>519520.9293420344</v>
+        <v>518249.3921049054</v>
       </c>
     </row>
     <row r="5">
@@ -26425,16 +26425,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56772.276</v>
+        <v>56856.345</v>
       </c>
       <c r="C5" t="n">
         <v>56856.345</v>
       </c>
       <c r="D5" t="n">
-        <v>57585.945</v>
+        <v>57889.945</v>
       </c>
       <c r="E5" t="n">
-        <v>54813.171</v>
+        <v>54729.102</v>
       </c>
       <c r="F5" t="n">
         <v>57167.103</v>
@@ -26455,7 +26455,7 @@
         <v>48977.128</v>
       </c>
       <c r="L5" t="n">
-        <v>57242.911</v>
+        <v>56938.911</v>
       </c>
       <c r="M5" t="n">
         <v>56652.925</v>
@@ -26467,7 +26467,7 @@
         <v>47237.197</v>
       </c>
       <c r="P5" t="n">
-        <v>44883.265</v>
+        <v>44799.196</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>483494.6536954664</v>
+        <v>483183.9679533506</v>
       </c>
       <c r="C6" t="n">
-        <v>703634.4588337095</v>
+        <v>704448.8675071825</v>
       </c>
       <c r="D6" t="n">
-        <v>704130.7265737284</v>
+        <v>703090.2873335282</v>
       </c>
       <c r="E6" t="n">
-        <v>396357.049246908</v>
+        <v>398285.9553414403</v>
       </c>
       <c r="F6" t="n">
-        <v>683200.4173841679</v>
+        <v>682415.4937578967</v>
       </c>
       <c r="G6" t="n">
-        <v>700843.7080901457</v>
+        <v>700058.7844638744</v>
       </c>
       <c r="H6" t="n">
-        <v>716471.5275262978</v>
+        <v>717286.6039000273</v>
       </c>
       <c r="I6" t="n">
-        <v>719302.1778312962</v>
+        <v>719317.25420503</v>
       </c>
       <c r="J6" t="n">
-        <v>337108.3666013761</v>
+        <v>337922.7530181743</v>
       </c>
       <c r="K6" t="n">
-        <v>637255.1362585723</v>
+        <v>636469.5226753701</v>
       </c>
       <c r="L6" t="n">
-        <v>624972.1023081654</v>
+        <v>624182.1171502545</v>
       </c>
       <c r="M6" t="n">
-        <v>721417.2683850646</v>
+        <v>722230.9871016071</v>
       </c>
       <c r="N6" t="n">
-        <v>729129.6770388237</v>
+        <v>729143.3957553661</v>
       </c>
       <c r="O6" t="n">
-        <v>538853.2877417699</v>
+        <v>539667.0064583117</v>
       </c>
       <c r="P6" t="n">
-        <v>629319.4468949775</v>
+        <v>628064.8380321063</v>
       </c>
     </row>
   </sheetData>
@@ -26755,7 +26755,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C2" t="n">
         <v>405</v>
@@ -26764,7 +26764,7 @@
         <v>405</v>
       </c>
       <c r="E2" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F2" t="n">
         <v>387</v>
@@ -26797,7 +26797,7 @@
         <v>313</v>
       </c>
       <c r="P2" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -26865,7 +26865,7 @@
         <v>340</v>
       </c>
       <c r="D4" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E4" t="n">
         <v>370</v>
@@ -26889,7 +26889,7 @@
         <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M4" t="n">
         <v>309</v>
@@ -26972,46 +26972,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27082,10 +27082,10 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>309</v>
@@ -27204,34 +27204,34 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -27323,10 +27323,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27433,19 +27433,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E2" t="n">
-        <v>404.0000000000005</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
-        <v>404</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
         <v>403.36340243777</v>
@@ -27484,25 +27484,25 @@
         <v>226.1308902855809</v>
       </c>
       <c r="S2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="U2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="V2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="W2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="X2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Y2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H3" t="n">
         <v>330.1322758656664</v>
       </c>
       <c r="I3" t="n">
-        <v>209.8688387215372</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,25 +27560,25 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>404</v>
+        <v>194.1861746508699</v>
       </c>
       <c r="S3" t="n">
-        <v>404</v>
+        <v>230.9638042667607</v>
       </c>
       <c r="T3" t="n">
-        <v>404.0000000000005</v>
+        <v>404.5081237080798</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1964918356584</v>
+        <v>60.19649183565845</v>
       </c>
       <c r="V3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="W3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="X3" t="n">
-        <v>139.9542496642467</v>
+        <v>405</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>404</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27606,13 +27606,13 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>293.3004767879511</v>
+        <v>380.9553550127408</v>
       </c>
       <c r="H4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I4" t="n">
-        <v>171.3189638168396</v>
+        <v>405</v>
       </c>
       <c r="J4" t="n">
         <v>362.7747521145963</v>
@@ -27621,34 +27621,34 @@
         <v>267.9889705224545</v>
       </c>
       <c r="L4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="S4" t="n">
         <v>359.2937092110521</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2694845390446</v>
+        <v>405</v>
       </c>
       <c r="U4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>404</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>404</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>44.55655664632661</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27758,10 +27758,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>2.672097221912622</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5287434221972</v>
@@ -27794,19 +27794,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R6" t="n">
-        <v>405</v>
+        <v>194.1861746508699</v>
       </c>
       <c r="S6" t="n">
-        <v>405</v>
+        <v>214.9231721528571</v>
       </c>
       <c r="T6" t="n">
         <v>404.5081237080798</v>
       </c>
       <c r="U6" t="n">
-        <v>400.1964918356584</v>
+        <v>60.19649183565845</v>
       </c>
       <c r="V6" t="n">
         <v>405</v>
@@ -27815,7 +27815,7 @@
         <v>405</v>
       </c>
       <c r="X6" t="n">
-        <v>149.91738253397</v>
+        <v>405</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,25 +27828,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>346.5378217158339</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>405</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>405</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>405</v>
       </c>
       <c r="G7" t="n">
-        <v>405</v>
+        <v>244.8671515300546</v>
       </c>
       <c r="H7" t="n">
-        <v>399.5360167585197</v>
+        <v>227.1999129868645</v>
       </c>
       <c r="I7" t="n">
         <v>171.3189638168396</v>
@@ -27879,10 +27879,10 @@
         <v>405</v>
       </c>
       <c r="S7" t="n">
-        <v>359.2937092110521</v>
+        <v>405</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2694845390446</v>
+        <v>405</v>
       </c>
       <c r="U7" t="n">
         <v>405</v>
@@ -27894,10 +27894,10 @@
         <v>405</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>405</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
@@ -27919,13 +27919,13 @@
         <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080118</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
         <v>403.36340243777</v>
       </c>
       <c r="H8" t="n">
-        <v>403.9749149849345</v>
+        <v>402.1774657513823</v>
       </c>
       <c r="I8" t="n">
         <v>134.8926370696193</v>
@@ -27995,10 +27995,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.5287434221972</v>
@@ -28046,13 +28046,13 @@
         <v>400.1964918356584</v>
       </c>
       <c r="V9" t="n">
-        <v>405</v>
+        <v>57.51066719151319</v>
       </c>
       <c r="W9" t="n">
-        <v>405</v>
+        <v>75.37314290982155</v>
       </c>
       <c r="X9" t="n">
-        <v>315.8887184774204</v>
+        <v>291.292568816296</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>405</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>390.5865031850843</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -28086,16 +28086,16 @@
         <v>227.1999129868645</v>
       </c>
       <c r="I10" t="n">
-        <v>171.3189638168396</v>
+        <v>218.5945419642583</v>
       </c>
       <c r="J10" t="n">
-        <v>22.77475211459628</v>
+        <v>379.7747521146032</v>
       </c>
       <c r="K10" t="n">
-        <v>267.9889705224545</v>
+        <v>405</v>
       </c>
       <c r="L10" t="n">
-        <v>397.2739888135169</v>
+        <v>405</v>
       </c>
       <c r="M10" t="n">
         <v>405</v>
@@ -28119,7 +28119,7 @@
         <v>359.2937092110521</v>
       </c>
       <c r="T10" t="n">
-        <v>405</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U10" t="n">
         <v>405</v>
@@ -28134,7 +28134,7 @@
         <v>405</v>
       </c>
       <c r="Y10" t="n">
-        <v>405</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28144,25 +28144,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I11" t="n">
         <v>134.8926370696193</v>
@@ -28195,25 +28195,25 @@
         <v>226.1308902855809</v>
       </c>
       <c r="S11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="W11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="X11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Y11" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
@@ -28223,25 +28223,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>359</v>
+        <v>14.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>325.5287434221972</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.413990685390957</v>
+        <v>330.1322758656664</v>
       </c>
       <c r="I12" t="n">
         <v>209.8688387215372</v>
@@ -28268,31 +28268,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="W12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="X12" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Y12" t="n">
-        <v>359</v>
+        <v>224.4100109812615</v>
       </c>
     </row>
     <row r="13">
@@ -28302,76 +28302,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E13" t="n">
-        <v>359</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H13" t="n">
-        <v>259.5159207389919</v>
+        <v>358</v>
       </c>
       <c r="I13" t="n">
         <v>171.3189638168396</v>
       </c>
       <c r="J13" t="n">
-        <v>22.77475211459628</v>
+        <v>331.9173706563287</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U13" t="n">
-        <v>359</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="W13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="X13" t="n">
-        <v>359</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y13" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14">
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>340.4784160596436</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
@@ -28505,22 +28505,22 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>164.1861746508699</v>
       </c>
       <c r="S15" t="n">
-        <v>236.022200168912</v>
+        <v>92.64862260612074</v>
       </c>
       <c r="T15" t="n">
         <v>387</v>
       </c>
       <c r="U15" t="n">
+        <v>30.19649183565845</v>
+      </c>
+      <c r="V15" t="n">
         <v>387</v>
-      </c>
-      <c r="V15" t="n">
-        <v>44.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>387</v>
@@ -28539,25 +28539,25 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C16" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D16" t="n">
+        <v>307.0007076055096</v>
+      </c>
+      <c r="E16" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F16" t="n">
         <v>387</v>
       </c>
-      <c r="C16" t="n">
+      <c r="G16" t="n">
         <v>387</v>
       </c>
-      <c r="D16" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E16" t="n">
-        <v>383.8234914098277</v>
-      </c>
-      <c r="F16" t="n">
-        <v>274.3828559677419</v>
-      </c>
-      <c r="G16" t="n">
-        <v>244.8671515300546</v>
-      </c>
       <c r="H16" t="n">
-        <v>227.1999129868645</v>
+        <v>387</v>
       </c>
       <c r="I16" t="n">
         <v>171.3189638168396</v>
@@ -28566,7 +28566,7 @@
         <v>22.77475211459628</v>
       </c>
       <c r="K16" t="n">
-        <v>387</v>
+        <v>267.9889705224545</v>
       </c>
       <c r="L16" t="n">
         <v>387</v>
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>88.02173299601907</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -28751,13 +28751,13 @@
         <v>401</v>
       </c>
       <c r="T18" t="n">
-        <v>99.85459671265301</v>
+        <v>401</v>
       </c>
       <c r="U18" t="n">
-        <v>30.19649183565845</v>
+        <v>400.1964918356584</v>
       </c>
       <c r="V18" t="n">
-        <v>44.51066719152016</v>
+        <v>401</v>
       </c>
       <c r="W18" t="n">
         <v>401</v>
@@ -28766,7 +28766,7 @@
         <v>401</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>29.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -28776,13 +28776,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>401</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C19" t="n">
         <v>401</v>
       </c>
       <c r="D19" t="n">
-        <v>401</v>
+        <v>352.0410318109495</v>
       </c>
       <c r="E19" t="n">
         <v>401</v>
@@ -28794,16 +28794,16 @@
         <v>244.8671515300546</v>
       </c>
       <c r="H19" t="n">
-        <v>355.328618913878</v>
+        <v>227.1999129868645</v>
       </c>
       <c r="I19" t="n">
-        <v>171.3189638168396</v>
+        <v>401</v>
       </c>
       <c r="J19" t="n">
-        <v>22.77475211459628</v>
+        <v>392.7747521145963</v>
       </c>
       <c r="K19" t="n">
-        <v>267.9889705224545</v>
+        <v>401</v>
       </c>
       <c r="L19" t="n">
         <v>401</v>
@@ -28839,13 +28839,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W19" t="n">
-        <v>401</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X19" t="n">
-        <v>401</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y19" t="n">
-        <v>401</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="20">
@@ -28934,25 +28934,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>262.4597237232678</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>325.5287434221972</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>330.1322758656664</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>209.8688387215372</v>
@@ -28982,13 +28982,13 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R21" t="n">
-        <v>401</v>
+        <v>164.1861746508699</v>
       </c>
       <c r="S21" t="n">
         <v>401</v>
       </c>
       <c r="T21" t="n">
-        <v>401</v>
+        <v>119.6683151488003</v>
       </c>
       <c r="U21" t="n">
         <v>400.1964918356584</v>
@@ -29025,25 +29025,25 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F22" t="n">
-        <v>274.3828559677419</v>
+        <v>401</v>
       </c>
       <c r="G22" t="n">
         <v>244.8671515300546</v>
       </c>
       <c r="H22" t="n">
+        <v>227.1999129868645</v>
+      </c>
+      <c r="I22" t="n">
         <v>401</v>
-      </c>
-      <c r="I22" t="n">
-        <v>171.3189638168396</v>
       </c>
       <c r="J22" t="n">
         <v>22.77475211459628</v>
       </c>
       <c r="K22" t="n">
-        <v>267.9889705224545</v>
+        <v>401</v>
       </c>
       <c r="L22" t="n">
-        <v>397.2739888135169</v>
+        <v>401</v>
       </c>
       <c r="M22" t="n">
         <v>401</v>
@@ -29064,16 +29064,16 @@
         <v>401</v>
       </c>
       <c r="S22" t="n">
-        <v>359.2937092110521</v>
+        <v>401</v>
       </c>
       <c r="T22" t="n">
         <v>209.2694845390446</v>
       </c>
       <c r="U22" t="n">
-        <v>401</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V22" t="n">
-        <v>401</v>
+        <v>234.6502703175749</v>
       </c>
       <c r="W22" t="n">
         <v>401</v>
@@ -29082,7 +29082,7 @@
         <v>401</v>
       </c>
       <c r="Y22" t="n">
-        <v>345.5404469030299</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23">
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>259.4238688391483</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>325.5287434221972</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R24" t="n">
         <v>401</v>
@@ -29231,16 +29231,16 @@
         <v>400.1964918356584</v>
       </c>
       <c r="V24" t="n">
-        <v>81.99212099434459</v>
+        <v>401</v>
       </c>
       <c r="W24" t="n">
-        <v>62.37314290982852</v>
+        <v>401</v>
       </c>
       <c r="X24" t="n">
         <v>401</v>
       </c>
       <c r="Y24" t="n">
-        <v>29.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -29253,13 +29253,13 @@
         <v>401</v>
       </c>
       <c r="C25" t="n">
-        <v>341.934426726636</v>
+        <v>401</v>
       </c>
       <c r="D25" t="n">
-        <v>285.5362180555555</v>
+        <v>401</v>
       </c>
       <c r="E25" t="n">
-        <v>280.9809048369565</v>
+        <v>286.8815888515886</v>
       </c>
       <c r="F25" t="n">
         <v>274.3828559677419</v>
@@ -29271,7 +29271,7 @@
         <v>227.1999129868645</v>
       </c>
       <c r="I25" t="n">
-        <v>171.3189638168396</v>
+        <v>401</v>
       </c>
       <c r="J25" t="n">
         <v>22.77475211459628</v>
@@ -29301,25 +29301,25 @@
         <v>401</v>
       </c>
       <c r="S25" t="n">
-        <v>359.2937092110521</v>
+        <v>401</v>
       </c>
       <c r="T25" t="n">
-        <v>209.2694845390446</v>
+        <v>401</v>
       </c>
       <c r="U25" t="n">
         <v>401</v>
       </c>
       <c r="V25" t="n">
-        <v>401</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
-        <v>401</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
-        <v>401</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y25" t="n">
-        <v>401</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -29426,7 +29426,7 @@
         <v>312</v>
       </c>
       <c r="H27" t="n">
-        <v>312</v>
+        <v>215.6496699508011</v>
       </c>
       <c r="I27" t="n">
         <v>209.8688387215372</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.82146334316757</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R27" t="n">
         <v>312</v>
@@ -29657,7 +29657,7 @@
         <v>312</v>
       </c>
       <c r="F30" t="n">
-        <v>312</v>
+        <v>215.649669950801</v>
       </c>
       <c r="G30" t="n">
         <v>312</v>
@@ -29666,7 +29666,7 @@
         <v>312</v>
       </c>
       <c r="I30" t="n">
-        <v>113.5185086723382</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>209.418285312179</v>
+        <v>226.1308902855809</v>
       </c>
       <c r="S32" t="n">
         <v>419</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>62.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>39.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29903,7 +29903,7 @@
         <v>330.1322758656664</v>
       </c>
       <c r="I33" t="n">
-        <v>209.8688387215372</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,10 +29927,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>419</v>
+        <v>342.4937117261103</v>
       </c>
       <c r="S33" t="n">
         <v>419</v>
@@ -29939,16 +29939,16 @@
         <v>404.5081237080798</v>
       </c>
       <c r="U33" t="n">
-        <v>73.19649183565845</v>
+        <v>400.1964918356584</v>
       </c>
       <c r="V33" t="n">
-        <v>87.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>105.3731429098285</v>
+        <v>419</v>
       </c>
       <c r="X33" t="n">
-        <v>290.6759367023782</v>
+        <v>419</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29967,25 +29967,25 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>419</v>
       </c>
       <c r="E34" t="n">
-        <v>280.9809048369565</v>
+        <v>419</v>
       </c>
       <c r="F34" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G34" t="n">
-        <v>244.8671515300546</v>
+        <v>419</v>
       </c>
       <c r="H34" t="n">
-        <v>419</v>
+        <v>238.8313809185249</v>
       </c>
       <c r="I34" t="n">
         <v>419</v>
       </c>
       <c r="J34" t="n">
-        <v>132.4400950797946</v>
+        <v>344.7747521145963</v>
       </c>
       <c r="K34" t="n">
         <v>419</v>
@@ -30015,10 +30015,10 @@
         <v>419</v>
       </c>
       <c r="T34" t="n">
-        <v>419</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U34" t="n">
-        <v>419</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V34" t="n">
         <v>199.1703102162162</v>
@@ -30128,16 +30128,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>61.88463078112051</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>30.6362423378657</v>
       </c>
       <c r="G36" t="n">
-        <v>16.52874342219716</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H36" t="n">
-        <v>21.13227586566641</v>
+        <v>330.1322758656664</v>
       </c>
       <c r="I36" t="n">
         <v>209.8688387215372</v>
@@ -30164,13 +30164,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>225.1861746508699</v>
+        <v>425</v>
       </c>
       <c r="S36" t="n">
-        <v>197.8545655159493</v>
+        <v>425</v>
       </c>
       <c r="T36" t="n">
         <v>404.5081237080798</v>
@@ -30188,7 +30188,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>90.39139276612323</v>
       </c>
     </row>
     <row r="37">
@@ -30204,31 +30204,31 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D37" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E37" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F37" t="n">
+        <v>305.9661681718883</v>
+      </c>
+      <c r="G37" t="n">
         <v>425</v>
       </c>
-      <c r="E37" t="n">
+      <c r="H37" t="n">
         <v>425</v>
       </c>
-      <c r="F37" t="n">
+      <c r="I37" t="n">
         <v>425</v>
       </c>
-      <c r="G37" t="n">
-        <v>366.0696276130316</v>
-      </c>
-      <c r="H37" t="n">
-        <v>227.1999129868645</v>
-      </c>
-      <c r="I37" t="n">
-        <v>171.3189638168396</v>
-      </c>
       <c r="J37" t="n">
-        <v>22.77475211459628</v>
+        <v>331.7747521146075</v>
       </c>
       <c r="K37" t="n">
-        <v>267.9889705224545</v>
+        <v>425</v>
       </c>
       <c r="L37" t="n">
-        <v>397.2739888135169</v>
+        <v>425</v>
       </c>
       <c r="M37" t="n">
         <v>425</v>
@@ -30249,13 +30249,13 @@
         <v>425</v>
       </c>
       <c r="S37" t="n">
-        <v>359.2937092110521</v>
+        <v>425</v>
       </c>
       <c r="T37" t="n">
-        <v>425</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U37" t="n">
-        <v>425</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
@@ -30264,7 +30264,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>425</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30359,7 +30359,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>52.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30368,16 +30368,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>30.63624233786604</v>
       </c>
       <c r="G39" t="n">
-        <v>325.5287434221972</v>
+        <v>16.52874342218637</v>
       </c>
       <c r="H39" t="n">
         <v>330.1322758656664</v>
       </c>
       <c r="I39" t="n">
-        <v>209.8688387215372</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,10 +30404,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>225.1861746508699</v>
+        <v>425</v>
       </c>
       <c r="S39" t="n">
-        <v>153.6486226061207</v>
+        <v>354.0813722807444</v>
       </c>
       <c r="T39" t="n">
         <v>404.5081237080798</v>
@@ -30416,7 +30416,7 @@
         <v>400.1964918356584</v>
       </c>
       <c r="V39" t="n">
-        <v>295.8884034937151</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
         <v>425</v>
@@ -30696,7 +30696,7 @@
         <v>313</v>
       </c>
       <c r="J43" t="n">
-        <v>313</v>
+        <v>249.6306377049669</v>
       </c>
       <c r="K43" t="n">
         <v>313</v>
@@ -30726,10 +30726,10 @@
         <v>313</v>
       </c>
       <c r="T43" t="n">
-        <v>209.2694845390446</v>
+        <v>313</v>
       </c>
       <c r="U43" t="n">
-        <v>287.8047985960297</v>
+        <v>313</v>
       </c>
       <c r="V43" t="n">
         <v>313</v>
@@ -30738,7 +30738,7 @@
         <v>313</v>
       </c>
       <c r="X43" t="n">
-        <v>313</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y43" t="n">
         <v>313</v>
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I44" t="n">
         <v>134.8926370696193</v>
@@ -30802,25 +30802,25 @@
         <v>226.1308902855809</v>
       </c>
       <c r="S44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Y44" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45">
@@ -30830,25 +30830,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I45" t="n">
         <v>209.8688387215372</v>
@@ -30878,28 +30878,28 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Y45" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Y46" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -34728,10 +34728,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5.24124134229736e-13</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.497171492763364e-14</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -34746,10 +34746,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>50.11444221105528</v>
+        <v>207.7249325344634</v>
       </c>
       <c r="L2" t="n">
-        <v>219.7818873083327</v>
+        <v>62.17139698492463</v>
       </c>
       <c r="M2" t="n">
         <v>340</v>
@@ -34825,7 +34825,7 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K3" t="n">
-        <v>105.940384476271</v>
+        <v>225.1422131313574</v>
       </c>
       <c r="L3" t="n">
         <v>319.8601489335927</v>
@@ -34837,7 +34837,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O3" t="n">
-        <v>291.6099086951992</v>
+        <v>172.4080800401129</v>
       </c>
       <c r="P3" t="n">
         <v>153.9181177222004</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>131.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34892,13 +34892,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>48.43332525789653</v>
+        <v>136.0882034826862</v>
       </c>
       <c r="H4" t="n">
-        <v>176.8000870131355</v>
+        <v>177.8000870131355</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>233.6810361831604</v>
       </c>
       <c r="J4" t="n">
         <v>340</v>
@@ -34907,7 +34907,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6.726011186483106</v>
+        <v>7.726011186483106</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,10 +34931,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>195.7305154609554</v>
       </c>
       <c r="U4" t="n">
-        <v>253.0512480698044</v>
+        <v>254.0512480698044</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>156.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>116.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -35059,13 +35059,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.1238703886191</v>
+        <v>25.92204173353273</v>
       </c>
       <c r="K6" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L6" t="n">
-        <v>200.6583202785063</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M6" t="n">
         <v>140.3600421645043</v>
@@ -35114,25 +35114,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>59.42402137875525</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>119.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>124.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>130.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>160.1328484699454</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.3361037716552</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>45.70629078894785</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>195.7305154609554</v>
       </c>
       <c r="U7" t="n">
         <v>254.0512480698044</v>
@@ -35180,10 +35180,10 @@
         <v>178.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>157.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>117.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>352.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>50.11444221105529</v>
+        <v>357</v>
       </c>
       <c r="L8" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="M8" t="n">
-        <v>352.0000000000009</v>
+        <v>357.000000000007</v>
       </c>
       <c r="N8" t="n">
-        <v>231.2970388234826</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>286.2094608325124</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,13 +35296,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.1238703886191</v>
+        <v>93.23517304666403</v>
       </c>
       <c r="K9" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L9" t="n">
-        <v>248.1734717936578</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M9" t="n">
         <v>140.3600421645043</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>117.8612565370396</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -35372,16 +35372,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>47.27557814741869</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>357.000000000007</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>137.0110294775455</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.726011186483124</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>195.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>254.0512480698044</v>
@@ -35420,7 +35420,7 @@
         <v>157.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>117.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35545,10 +35545,10 @@
         <v>140.3600421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>189.0362040150322</v>
+        <v>189.4501538822398</v>
       </c>
       <c r="O12" t="n">
-        <v>291.6099086951992</v>
+        <v>291.1959588280469</v>
       </c>
       <c r="P12" t="n">
         <v>153.9181177222004</v>
@@ -35588,34 +35588,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.88619966292134</v>
+        <v>70.88619966292134</v>
       </c>
       <c r="C13" t="n">
-        <v>86.27475335195533</v>
+        <v>85.27475335195533</v>
       </c>
       <c r="D13" t="n">
-        <v>73.46378194444452</v>
+        <v>72.46378194444452</v>
       </c>
       <c r="E13" t="n">
-        <v>78.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>84.61714403225807</v>
+        <v>83.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>114.1328484699454</v>
+        <v>113.1328484699454</v>
       </c>
       <c r="H13" t="n">
-        <v>32.31600775212735</v>
+        <v>130.8000870131355</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>309.1426185417325</v>
       </c>
       <c r="K13" t="n">
-        <v>91.01102947754548</v>
+        <v>90.01102947754548</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35642,22 +35642,22 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>149.7305154609554</v>
+        <v>148.7305154609554</v>
       </c>
       <c r="U13" t="n">
-        <v>208.0512480698044</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>159.8296897837838</v>
+        <v>158.8296897837838</v>
       </c>
       <c r="W13" t="n">
-        <v>132.6271901612903</v>
+        <v>131.6271901612903</v>
       </c>
       <c r="X13" t="n">
-        <v>111.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>71.53464715053764</v>
+        <v>70.53464715053764</v>
       </c>
     </row>
     <row r="14">
@@ -35691,25 +35691,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="K14" t="n">
-        <v>236.5128113223423</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L14" t="n">
-        <v>62.17139698492463</v>
+        <v>62.17139698492468</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>242.7646658545251</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>370</v>
-      </c>
-      <c r="N14" t="n">
-        <v>370</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>56.36629674323819</v>
       </c>
       <c r="Q14" t="n">
         <v>370</v>
@@ -35825,25 +35825,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>99.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>114.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>21.46448954995413</v>
       </c>
       <c r="E16" t="n">
-        <v>102.8425865728712</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>112.6171440322581</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>142.1328484699454</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>159.8000870131355</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>119.0110294775455</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>236.5128113223423</v>
+        <v>50.11444221105528</v>
       </c>
       <c r="L17" t="n">
-        <v>62.17139698492463</v>
+        <v>248.5697660962117</v>
       </c>
       <c r="M17" t="n">
         <v>370</v>
@@ -36013,7 +36013,7 @@
         <v>225.1422131313574</v>
       </c>
       <c r="L18" t="n">
-        <v>319.8601489335927</v>
+        <v>319.446199066385</v>
       </c>
       <c r="M18" t="n">
         <v>140.3600421645043</v>
@@ -36022,7 +36022,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O18" t="n">
-        <v>291.1959588279915</v>
+        <v>291.6099086951992</v>
       </c>
       <c r="P18" t="n">
         <v>153.9181177222004</v>
@@ -36062,13 +36062,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>128.2747533519553</v>
       </c>
       <c r="D19" t="n">
-        <v>115.4637819444445</v>
+        <v>66.50481375539404</v>
       </c>
       <c r="E19" t="n">
         <v>120.0190951630435</v>
@@ -36080,19 +36080,19 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>128.1287059270134</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>229.6810361831604</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>133.0110294775455</v>
       </c>
       <c r="L19" t="n">
-        <v>3.726011186483124</v>
+        <v>3.726011186483106</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -36125,13 +36125,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>174.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>153.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>113.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -36250,13 +36250,13 @@
         <v>225.1422131313574</v>
       </c>
       <c r="L21" t="n">
-        <v>319.446199066385</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M21" t="n">
         <v>140.3600421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>189.4501538822398</v>
+        <v>189.0362040150322</v>
       </c>
       <c r="O21" t="n">
         <v>291.6099086951992</v>
@@ -36311,25 +36311,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>126.6171440322581</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>173.8000870131355</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>229.6810361831604</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>133.0110294775455</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.726011186483124</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36350,16 +36350,16 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>41.70629078894784</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>250.0512480698044</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>201.8296897837838</v>
+        <v>35.47996010135871</v>
       </c>
       <c r="W22" t="n">
         <v>174.6271901612903</v>
@@ -36368,7 +36368,7 @@
         <v>153.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>58.07509405356752</v>
+        <v>113.5346471505376</v>
       </c>
     </row>
     <row r="23">
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>50.11444221105529</v>
+        <v>50.11444221105528</v>
       </c>
       <c r="L23" t="n">
-        <v>62.17139698492468</v>
+        <v>248.5697660962668</v>
       </c>
       <c r="M23" t="n">
-        <v>370</v>
+        <v>370.0000000000101</v>
       </c>
       <c r="N23" t="n">
-        <v>370</v>
+        <v>370.0000000000101</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q23" t="n">
-        <v>186.3983691112869</v>
+        <v>370.0000000000101</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36487,7 +36487,7 @@
         <v>225.1422131313574</v>
       </c>
       <c r="L24" t="n">
-        <v>319.446199066385</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M24" t="n">
         <v>140.3600421645043</v>
@@ -36496,7 +36496,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O24" t="n">
-        <v>291.6099086951992</v>
+        <v>291.195958828077</v>
       </c>
       <c r="P24" t="n">
         <v>153.9181177222004</v>
@@ -36539,13 +36539,13 @@
         <v>113.8861996629213</v>
       </c>
       <c r="C25" t="n">
-        <v>69.20918007859136</v>
+        <v>128.2747533519553</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>115.4637819444445</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5.900684014632088</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -36557,7 +36557,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>229.6810361831604</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -36566,7 +36566,7 @@
         <v>133.0110294775455</v>
       </c>
       <c r="L25" t="n">
-        <v>3.726011186483106</v>
+        <v>3.726011186483124</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -36587,25 +36587,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>41.70629078894784</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>191.7305154609554</v>
       </c>
       <c r="U25" t="n">
         <v>250.0512480698044</v>
       </c>
       <c r="V25" t="n">
-        <v>201.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>174.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>153.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>113.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>339</v>
+        <v>339.0000000000178</v>
       </c>
       <c r="K26" t="n">
         <v>50.11444221105529</v>
       </c>
       <c r="L26" t="n">
-        <v>339</v>
+        <v>62.17139698492463</v>
       </c>
       <c r="M26" t="n">
-        <v>218.8222913487368</v>
+        <v>339.0000000000178</v>
       </c>
       <c r="N26" t="n">
-        <v>339</v>
+        <v>156.6508943637588</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -36660,7 +36660,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>339.0000000000178</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36733,10 +36733,10 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O27" t="n">
-        <v>168.4484840805168</v>
+        <v>291.6099086951992</v>
       </c>
       <c r="P27" t="n">
-        <v>153.9181177222004</v>
+        <v>30.75669310751804</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>339</v>
+        <v>339.0000000000115</v>
       </c>
       <c r="K29" t="n">
-        <v>339.0000000000001</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L29" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M29" t="n">
-        <v>206.7653365748674</v>
+        <v>339.0000000000115</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>156.6508943637774</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q29" t="n">
-        <v>339</v>
+        <v>339.0000000000115</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>289.2252478854037</v>
       </c>
       <c r="K31" t="n">
-        <v>44.01102947754549</v>
+        <v>44.01102947754548</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>50.11444221105529</v>
+        <v>322</v>
       </c>
       <c r="L32" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M32" t="n">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N32" t="n">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -37134,7 +37134,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q32" t="n">
-        <v>145.1357428486607</v>
+        <v>190.4522052617361</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
         <v>225.1422131313574</v>
       </c>
       <c r="L33" t="n">
-        <v>303.1016905259592</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M33" t="n">
         <v>140.3600421645043</v>
@@ -37207,10 +37207,10 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O33" t="n">
-        <v>291.6099086951992</v>
+        <v>101.1353527673857</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37253,25 +37253,25 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>133.4637819444445</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>138.0190951630435</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>174.1328484699454</v>
       </c>
       <c r="H34" t="n">
-        <v>191.8000870131355</v>
+        <v>11.6314679316604</v>
       </c>
       <c r="I34" t="n">
         <v>247.6810361831604</v>
       </c>
       <c r="J34" t="n">
-        <v>109.6653429651983</v>
+        <v>322</v>
       </c>
       <c r="K34" t="n">
         <v>151.0110294775455</v>
@@ -37301,10 +37301,10 @@
         <v>59.70629078894784</v>
       </c>
       <c r="T34" t="n">
-        <v>209.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>268.0512480698043</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>50.11444221105528</v>
+      </c>
+      <c r="L35" t="n">
         <v>309</v>
       </c>
-      <c r="K35" t="n">
-        <v>50.11444221105529</v>
-      </c>
-      <c r="L35" t="n">
-        <v>62.17139698492463</v>
-      </c>
       <c r="M35" t="n">
-        <v>309</v>
+        <v>190.0344125608359</v>
       </c>
       <c r="N35" t="n">
-        <v>127.8630155759333</v>
+        <v>309.0000000000111</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q35" t="n">
-        <v>309</v>
+        <v>309.0000000000111</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,13 +37429,13 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>145.1238703886191</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L36" t="n">
-        <v>231.8289632532319</v>
+        <v>223.0347159196506</v>
       </c>
       <c r="M36" t="n">
         <v>140.3600421645043</v>
@@ -37447,7 +37447,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37490,31 +37490,31 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>139.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>144.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>150.6171440322581</v>
+        <v>31.58331220414639</v>
       </c>
       <c r="G37" t="n">
-        <v>121.202476082977</v>
+        <v>180.1328484699454</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>197.8000870131355</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>253.6810361831604</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>309.0000000000111</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>157.0110294775455</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>27.72601118648312</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,13 +37535,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>65.70629078894784</v>
       </c>
       <c r="T37" t="n">
-        <v>215.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>274.0512480698044</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -37550,7 +37550,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>177.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>50.11444221105529</v>
+        <v>177.9774577869561</v>
       </c>
       <c r="L38" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M38" t="n">
-        <v>309</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="N38" t="n">
-        <v>309</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -37608,7 +37608,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q38" t="n">
-        <v>127.8630155759333</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37669,10 +37669,10 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K39" t="n">
-        <v>147.9711763845892</v>
+        <v>225.1422131313574</v>
       </c>
       <c r="L39" t="n">
-        <v>309</v>
+        <v>309.0000000000108</v>
       </c>
       <c r="M39" t="n">
         <v>140.3600421645043</v>
@@ -37681,7 +37681,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O39" t="n">
-        <v>291.6099086951992</v>
+        <v>214.4388719484202</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -37827,25 +37827,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>50.11444221105528</v>
+        <v>309</v>
       </c>
       <c r="L41" t="n">
-        <v>62.17139698492461</v>
+        <v>309</v>
       </c>
       <c r="M41" t="n">
-        <v>127.8630155759332</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>309</v>
+        <v>309.000000000011</v>
       </c>
       <c r="O41" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>56.36629674323819</v>
       </c>
       <c r="Q41" t="n">
-        <v>309</v>
+        <v>240.1488547719023</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,10 +37906,10 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>225.1422131313574</v>
       </c>
       <c r="L42" t="n">
-        <v>303.0530586623889</v>
+        <v>231.8289632532319</v>
       </c>
       <c r="M42" t="n">
         <v>140.3600421645043</v>
@@ -37921,7 +37921,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P42" t="n">
-        <v>153.9181177222004</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>141.6810361831604</v>
       </c>
       <c r="J43" t="n">
-        <v>290.2252478854037</v>
+        <v>226.8558855903705</v>
       </c>
       <c r="K43" t="n">
         <v>45.01102947754548</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>103.7305154609554</v>
       </c>
       <c r="U43" t="n">
-        <v>136.8560466658341</v>
+        <v>162.0512480698044</v>
       </c>
       <c r="V43" t="n">
         <v>113.8296897837838</v>
@@ -38024,7 +38024,7 @@
         <v>86.62719016129032</v>
       </c>
       <c r="X43" t="n">
-        <v>65.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>25.53464715053764</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>309</v>
+        <v>309.000000000011</v>
       </c>
       <c r="K44" t="n">
         <v>50.11444221105529</v>
@@ -38070,19 +38070,19 @@
         <v>62.17139698492463</v>
       </c>
       <c r="M44" t="n">
-        <v>309</v>
+        <v>309.000000000011</v>
       </c>
       <c r="N44" t="n">
-        <v>127.8630155759333</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>309.000000000011</v>
       </c>
       <c r="P44" t="n">
         <v>56.36629674323819</v>
       </c>
       <c r="Q44" t="n">
-        <v>309</v>
+        <v>127.8630155759004</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>145.1238703886191</v>
       </c>
       <c r="K45" t="n">
-        <v>139.1769290510079</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>309</v>
+        <v>303.0530586623889</v>
       </c>
       <c r="M45" t="n">
         <v>140.3600421645043</v>
@@ -38198,31 +38198,31 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>12.27475335195533</v>
+        <v>11.27475335195533</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>4.01909516304346</v>
+        <v>3.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>10.61714403225807</v>
+        <v>9.617144032258068</v>
       </c>
       <c r="G46" t="n">
-        <v>40.13284846994538</v>
+        <v>39.13284846994537</v>
       </c>
       <c r="H46" t="n">
-        <v>57.80008701313548</v>
+        <v>56.80008701313548</v>
       </c>
       <c r="I46" t="n">
-        <v>113.6810361831604</v>
+        <v>112.6810361831604</v>
       </c>
       <c r="J46" t="n">
-        <v>262.2252478854037</v>
+        <v>261.2252478854037</v>
       </c>
       <c r="K46" t="n">
-        <v>17.01102947754548</v>
+        <v>16.01102947754549</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,19 +38249,19 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>75.7305154609554</v>
+        <v>74.73051546095539</v>
       </c>
       <c r="U46" t="n">
-        <v>134.0512480698044</v>
+        <v>133.0512480698044</v>
       </c>
       <c r="V46" t="n">
-        <v>85.82968978378381</v>
+        <v>84.82968978378381</v>
       </c>
       <c r="W46" t="n">
-        <v>58.62719016129032</v>
+        <v>57.62719016129032</v>
       </c>
       <c r="X46" t="n">
-        <v>37.55635456989245</v>
+        <v>36.55635456989245</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
